--- a/Excel-files/PendingSales1.xlsx
+++ b/Excel-files/PendingSales1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <si>
     <t>DateSelector</t>
   </si>
@@ -49,1036 +49,862 @@
     <t>MSI</t>
   </si>
   <si>
-    <t>Single Family Residence</t>
-  </si>
-  <si>
-    <t>1933</t>
-  </si>
-  <si>
-    <t>Residential Income</t>
+    <t>ESTERO</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>FORT MYERS BEACH</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>FORT MYERS</t>
+  </si>
+  <si>
+    <t>665</t>
+  </si>
+  <si>
+    <t>BONITA SPRINGS</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>842</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>908</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>871</t>
+  </si>
+  <si>
+    <t>757</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>681</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>654</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>618</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>545</t>
+  </si>
+  <si>
+    <t>554</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>493</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>653</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>773</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>852</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>789</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>748</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>692</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>667</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>659</t>
+  </si>
+  <si>
+    <t>683</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>697</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>542</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>690</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>846</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>662</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>549</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>743</t>
+  </si>
+  <si>
+    <t>863</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>813</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>911</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>941</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>388</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>993</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>784</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>1365</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>529</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>526</t>
+  </si>
+  <si>
+    <t>1306</t>
+  </si>
+  <si>
+    <t>455</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>1169</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>881</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>883</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>796</t>
+  </si>
+  <si>
+    <t>886</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>890</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>891</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>990</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>83</t>
   </si>
   <si>
     <t>65</t>
   </si>
   <si>
-    <t>Condominium</t>
-  </si>
-  <si>
-    <t>1204</t>
-  </si>
-  <si>
-    <t>Land</t>
-  </si>
-  <si>
-    <t>613</t>
-  </si>
-  <si>
-    <t>676</t>
-  </si>
-  <si>
-    <t>1520</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>2365</t>
-  </si>
-  <si>
-    <t>70</t>
+    <t>717</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>706</t>
+  </si>
+  <si>
+    <t>621</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>534</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>555</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>481</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>684</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>823</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>398</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>786</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>693</t>
+  </si>
+  <si>
+    <t>644</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>622</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>592</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>536</t>
+  </si>
+  <si>
+    <t>469</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>503</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>611</t>
   </si>
   <si>
     <t>703</t>
   </si>
   <si>
-    <t>1680</t>
-  </si>
-  <si>
-    <t>2668</t>
-  </si>
-  <si>
-    <t>2585</t>
-  </si>
-  <si>
-    <t>726</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>1618</t>
-  </si>
-  <si>
-    <t>2386</t>
-  </si>
-  <si>
-    <t>1358</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>679</t>
-  </si>
-  <si>
-    <t>739</t>
-  </si>
-  <si>
-    <t>2065</t>
-  </si>
-  <si>
-    <t>1152</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>573</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>1974</t>
-  </si>
-  <si>
-    <t>557</t>
-  </si>
-  <si>
-    <t>1822</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>998</t>
-  </si>
-  <si>
-    <t>524</t>
-  </si>
-  <si>
-    <t>1768</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>882</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>1697</t>
+    <t>307</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>735</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>599</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>482</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>190</t>
   </si>
   <si>
     <t>546</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
-    <t>494</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>1545</t>
-  </si>
-  <si>
-    <t>873</t>
-  </si>
-  <si>
-    <t>466</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>740</t>
-  </si>
-  <si>
-    <t>1306</t>
-  </si>
-  <si>
-    <t>1750</t>
-  </si>
-  <si>
-    <t>1041</t>
-  </si>
-  <si>
-    <t>583</t>
-  </si>
-  <si>
-    <t>1441</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>644</t>
-  </si>
-  <si>
-    <t>2254</t>
-  </si>
-  <si>
-    <t>2596</t>
-  </si>
-  <si>
-    <t>1788</t>
-  </si>
-  <si>
-    <t>1574</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>547</t>
-  </si>
-  <si>
-    <t>2677</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>2373</t>
-  </si>
-  <si>
-    <t>1345</t>
-  </si>
-  <si>
-    <t>519</t>
-  </si>
-  <si>
-    <t>1250</t>
-  </si>
-  <si>
-    <t>2219</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>491</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>1037</t>
-  </si>
-  <si>
-    <t>515</t>
-  </si>
-  <si>
-    <t>1979</t>
-  </si>
-  <si>
-    <t>1924</t>
-  </si>
-  <si>
-    <t>481</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>1021</t>
-  </si>
-  <si>
-    <t>1043</t>
-  </si>
-  <si>
-    <t>2020</t>
+    <t>729</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>626</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>580</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>532</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>474</t>
+  </si>
+  <si>
+    <t>509</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>625</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>1171</t>
-  </si>
-  <si>
-    <t>622</t>
-  </si>
-  <si>
-    <t>2099</t>
-  </si>
-  <si>
-    <t>871</t>
-  </si>
-  <si>
-    <t>607</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>1597</t>
-  </si>
-  <si>
-    <t>627</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>1293</t>
-  </si>
-  <si>
-    <t>2217</t>
-  </si>
-  <si>
-    <t>748</t>
-  </si>
-  <si>
-    <t>2708</t>
-  </si>
-  <si>
-    <t>1693</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>562</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>832</t>
-  </si>
-  <si>
-    <t>1840</t>
-  </si>
-  <si>
-    <t>604</t>
-  </si>
-  <si>
-    <t>750</t>
-  </si>
-  <si>
-    <t>2478</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>3021</t>
-  </si>
-  <si>
-    <t>1382</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>1190</t>
-  </si>
-  <si>
-    <t>1391</t>
-  </si>
-  <si>
-    <t>3076</t>
-  </si>
-  <si>
-    <t>1551</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>3265</t>
-  </si>
-  <si>
-    <t>1320</t>
-  </si>
-  <si>
-    <t>1690</t>
-  </si>
-  <si>
-    <t>3389</t>
-  </si>
-  <si>
-    <t>1297</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>1799</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>3464</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>1867</t>
-  </si>
-  <si>
-    <t>3401</t>
-  </si>
-  <si>
-    <t>1076</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>1606</t>
-  </si>
-  <si>
-    <t>2860</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>1079</t>
-  </si>
-  <si>
-    <t>1683</t>
-  </si>
-  <si>
-    <t>3637</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>4412</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>3065</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>4547</t>
-  </si>
-  <si>
-    <t>3096</t>
-  </si>
-  <si>
-    <t>1829</t>
-  </si>
-  <si>
-    <t>4209</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>4018</t>
-  </si>
-  <si>
-    <t>2344</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>3347</t>
-  </si>
-  <si>
-    <t>1859</t>
-  </si>
-  <si>
-    <t>1440</t>
-  </si>
-  <si>
-    <t>3109</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>1194</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>1559</t>
-  </si>
-  <si>
-    <t>1187</t>
-  </si>
-  <si>
-    <t>3112</t>
-  </si>
-  <si>
-    <t>1105</t>
-  </si>
-  <si>
-    <t>1484</t>
-  </si>
-  <si>
-    <t>3078</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>3201</t>
-  </si>
-  <si>
-    <t>1632</t>
-  </si>
-  <si>
-    <t>1145</t>
-  </si>
-  <si>
-    <t>1129</t>
-  </si>
-  <si>
-    <t>3150</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1405</t>
-  </si>
-  <si>
-    <t>2730</t>
-  </si>
-  <si>
-    <t>1155</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>1742</t>
-  </si>
-  <si>
-    <t>1590</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>3299</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1732</t>
-  </si>
-  <si>
-    <t>2142</t>
-  </si>
-  <si>
-    <t>3724</t>
-  </si>
-  <si>
-    <t>2279</t>
-  </si>
-  <si>
-    <t>3699</t>
-  </si>
-  <si>
-    <t>1699</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1503</t>
-  </si>
-  <si>
-    <t>3436</t>
-  </si>
-  <si>
-    <t>2145</t>
-  </si>
-  <si>
-    <t>3045</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>1748</t>
-  </si>
-  <si>
-    <t>1279</t>
-  </si>
-  <si>
-    <t>2469</t>
-  </si>
-  <si>
-    <t>857</t>
-  </si>
-  <si>
-    <t>1381</t>
-  </si>
-  <si>
-    <t>2341</t>
-  </si>
-  <si>
-    <t>696</t>
-  </si>
-  <si>
-    <t>1266</t>
-  </si>
-  <si>
-    <t>1241</t>
-  </si>
-  <si>
-    <t>730</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1138</t>
-  </si>
-  <si>
-    <t>697</t>
-  </si>
-  <si>
-    <t>1962</t>
-  </si>
-  <si>
-    <t>1873</t>
-  </si>
-  <si>
-    <t>497</t>
-  </si>
-  <si>
-    <t>1084</t>
-  </si>
-  <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>1976</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>1790</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>504</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>2358</t>
-  </si>
-  <si>
-    <t>659</t>
-  </si>
-  <si>
-    <t>1343</t>
-  </si>
-  <si>
-    <t>2774</t>
-  </si>
-  <si>
-    <t>1688</t>
-  </si>
-  <si>
-    <t>835</t>
-  </si>
-  <si>
-    <t>893</t>
-  </si>
-  <si>
-    <t>2813</t>
-  </si>
-  <si>
-    <t>1767</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>2868</t>
-  </si>
-  <si>
-    <t>1599</t>
-  </si>
-  <si>
-    <t>977</t>
-  </si>
-  <si>
-    <t>2515</t>
-  </si>
-  <si>
-    <t>1317</t>
-  </si>
-  <si>
-    <t>877</t>
-  </si>
-  <si>
-    <t>2248</t>
-  </si>
-  <si>
-    <t>1094</t>
-  </si>
-  <si>
-    <t>929</t>
-  </si>
-  <si>
-    <t>2245</t>
-  </si>
-  <si>
-    <t>936</t>
-  </si>
-  <si>
-    <t>2055</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>895</t>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
-    <t>1853</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>773</t>
-  </si>
-  <si>
-    <t>912</t>
-  </si>
-  <si>
-    <t>1647</t>
-  </si>
-  <si>
-    <t>698</t>
-  </si>
-  <si>
-    <t>863</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>1369</t>
-  </si>
-  <si>
-    <t>787</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>1883</t>
-  </si>
-  <si>
-    <t>2454</t>
-  </si>
-  <si>
-    <t>837</t>
-  </si>
-  <si>
-    <t>1373</t>
-  </si>
-  <si>
-    <t>1462</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>764</t>
-  </si>
-  <si>
-    <t>2562</t>
-  </si>
-  <si>
-    <t>807</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>1275</t>
-  </si>
-  <si>
-    <t>2499</t>
-  </si>
-  <si>
-    <t>1028</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>606</t>
+    <t>768</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>332</t>
   </si>
   <si>
     <t>841</t>
   </si>
   <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>585</t>
-  </si>
-  <si>
-    <t>1879</t>
-  </si>
-  <si>
-    <t>780</t>
-  </si>
-  <si>
-    <t>733</t>
-  </si>
-  <si>
-    <t>631</t>
-  </si>
-  <si>
-    <t>1692</t>
-  </si>
-  <si>
-    <t>701</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>597</t>
-  </si>
-  <si>
-    <t>452</t>
-  </si>
-  <si>
-    <t>1430</t>
-  </si>
-  <si>
-    <t>594</t>
-  </si>
-  <si>
-    <t>1523</t>
-  </si>
-  <si>
-    <t>579</t>
-  </si>
-  <si>
-    <t>785</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>462</t>
-  </si>
-  <si>
-    <t>1267</t>
-  </si>
-  <si>
-    <t>641</t>
-  </si>
-  <si>
-    <t>1670</t>
-  </si>
-  <si>
-    <t>819</t>
-  </si>
-  <si>
-    <t>2182</t>
-  </si>
-  <si>
-    <t>1157</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>554</t>
-  </si>
-  <si>
-    <t>548</t>
-  </si>
-  <si>
-    <t>1223</t>
-  </si>
-  <si>
-    <t>2368</t>
-  </si>
-  <si>
-    <t>2269</t>
-  </si>
-  <si>
-    <t>1044</t>
-  </si>
-  <si>
-    <t>2176</t>
-  </si>
-  <si>
-    <t>438</t>
-  </si>
-  <si>
-    <t>909</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>408</t>
-  </si>
-  <si>
-    <t>810</t>
-  </si>
-  <si>
-    <t>372</t>
-  </si>
-  <si>
-    <t>804</t>
-  </si>
-  <si>
-    <t>1745</t>
-  </si>
-  <si>
-    <t>1781</t>
-  </si>
-  <si>
-    <t>774</t>
-  </si>
-  <si>
-    <t>388</t>
-  </si>
-  <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>751</t>
-  </si>
-  <si>
-    <t>407</t>
-  </si>
-  <si>
-    <t>1662</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>966</t>
-  </si>
-  <si>
-    <t>1785</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>793</t>
-  </si>
-  <si>
-    <t>1412</t>
-  </si>
-  <si>
-    <t>1173</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>1988</t>
-  </si>
-  <si>
-    <t>415</t>
-  </si>
-  <si>
-    <t>1476</t>
-  </si>
-  <si>
-    <t>479</t>
-  </si>
-  <si>
-    <t>2578</t>
-  </si>
-  <si>
-    <t>1560</t>
-  </si>
-  <si>
-    <t>2799</t>
-  </si>
-  <si>
-    <t>1518</t>
-  </si>
-  <si>
-    <t>2863</t>
-  </si>
-  <si>
-    <t>591</t>
+    <t>226</t>
+  </si>
+  <si>
+    <t>829</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1260,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.57421875" customWidth="1"/>
-    <col min="2" max="2" width="23.421875" customWidth="1"/>
+    <col min="2" max="2" width="19.28125" customWidth="1"/>
     <col min="3" max="4" width="14.57421875" customWidth="1"/>
     <col min="5" max="5" width="15.140625" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
@@ -1561,7 +1387,7 @@
         <v>43159</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -1599,7 +1425,7 @@
         <v>43159</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
@@ -1637,7 +1463,7 @@
         <v>43190</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
@@ -1656,7 +1482,7 @@
         <v>43190</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11"/>
       <c r="D11"/>
@@ -1675,7 +1501,7 @@
         <v>43190</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12"/>
       <c r="D12"/>
@@ -1713,7 +1539,7 @@
         <v>43220</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14"/>
       <c r="D14"/>
@@ -1732,7 +1558,7 @@
         <v>43220</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C15"/>
       <c r="D15"/>
@@ -1751,7 +1577,7 @@
         <v>43220</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C16"/>
       <c r="D16"/>
@@ -1789,7 +1615,7 @@
         <v>43251</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C18"/>
       <c r="D18"/>
@@ -1808,7 +1634,7 @@
         <v>43251</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19"/>
       <c r="D19"/>
@@ -1816,7 +1642,7 @@
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -1827,7 +1653,7 @@
         <v>43251</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C20"/>
       <c r="D20"/>
@@ -1835,7 +1661,7 @@
       <c r="F20"/>
       <c r="G20"/>
       <c r="H20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -1854,7 +1680,7 @@
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -1865,7 +1691,7 @@
         <v>43281</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C22"/>
       <c r="D22"/>
@@ -1873,7 +1699,7 @@
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -1903,7 +1729,7 @@
         <v>43281</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C24"/>
       <c r="D24"/>
@@ -1922,7 +1748,7 @@
         <v>43281</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C25"/>
       <c r="D25"/>
@@ -1941,7 +1767,7 @@
         <v>43312</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C26"/>
       <c r="D26"/>
@@ -1960,7 +1786,7 @@
         <v>43312</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C27"/>
       <c r="D27"/>
@@ -1998,7 +1824,7 @@
         <v>43312</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C29"/>
       <c r="D29"/>
@@ -2017,7 +1843,7 @@
         <v>43343</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C30"/>
       <c r="D30"/>
@@ -2036,7 +1862,7 @@
         <v>43343</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C31"/>
       <c r="D31"/>
@@ -2055,7 +1881,7 @@
         <v>43343</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -2074,7 +1900,7 @@
         <v>43343</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -2093,7 +1919,7 @@
         <v>43373</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C34"/>
       <c r="D34"/>
@@ -2131,7 +1957,7 @@
         <v>43373</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C36"/>
       <c r="D36"/>
@@ -2169,7 +1995,7 @@
         <v>43404</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C38"/>
       <c r="D38"/>
@@ -2207,7 +2033,7 @@
         <v>43404</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C40"/>
       <c r="D40"/>
@@ -2226,7 +2052,7 @@
         <v>43404</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C41"/>
       <c r="D41"/>
@@ -2245,7 +2071,7 @@
         <v>43434</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C42"/>
       <c r="D42"/>
@@ -2283,7 +2109,7 @@
         <v>43434</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C44"/>
       <c r="D44"/>
@@ -2302,7 +2128,7 @@
         <v>43434</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C45"/>
       <c r="D45"/>
@@ -2321,7 +2147,7 @@
         <v>43465</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C46"/>
       <c r="D46"/>
@@ -2340,7 +2166,7 @@
         <v>43465</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C47"/>
       <c r="D47"/>
@@ -2378,7 +2204,7 @@
         <v>43465</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C49"/>
       <c r="D49"/>
@@ -2386,7 +2212,7 @@
       <c r="F49"/>
       <c r="G49"/>
       <c r="H49" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="I49"/>
       <c r="J49"/>
@@ -2405,7 +2231,7 @@
       <c r="F50"/>
       <c r="G50"/>
       <c r="H50" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I50"/>
       <c r="J50"/>
@@ -2416,7 +2242,7 @@
         <v>43496</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C51"/>
       <c r="D51"/>
@@ -2435,7 +2261,7 @@
         <v>43496</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C52"/>
       <c r="D52"/>
@@ -2454,7 +2280,7 @@
         <v>43496</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C53"/>
       <c r="D53"/>
@@ -2473,7 +2299,7 @@
         <v>43524</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C54"/>
       <c r="D54"/>
@@ -2511,7 +2337,7 @@
         <v>43524</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C56"/>
       <c r="D56"/>
@@ -2549,7 +2375,7 @@
         <v>43555</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C58"/>
       <c r="D58"/>
@@ -2568,7 +2394,7 @@
         <v>43555</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C59"/>
       <c r="D59"/>
@@ -2595,7 +2421,7 @@
       <c r="F60"/>
       <c r="G60"/>
       <c r="H60" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I60"/>
       <c r="J60"/>
@@ -2606,7 +2432,7 @@
         <v>43555</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C61"/>
       <c r="D61"/>
@@ -2614,7 +2440,7 @@
       <c r="F61"/>
       <c r="G61"/>
       <c r="H61" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="I61"/>
       <c r="J61"/>
@@ -2633,7 +2459,7 @@
       <c r="F62"/>
       <c r="G62"/>
       <c r="H62" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I62"/>
       <c r="J62"/>
@@ -2652,7 +2478,7 @@
       <c r="F63"/>
       <c r="G63"/>
       <c r="H63" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I63"/>
       <c r="J63"/>
@@ -2671,7 +2497,7 @@
       <c r="F64"/>
       <c r="G64"/>
       <c r="H64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I64"/>
       <c r="J64"/>
@@ -2690,7 +2516,7 @@
       <c r="F65"/>
       <c r="G65"/>
       <c r="H65" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I65"/>
       <c r="J65"/>
@@ -2701,7 +2527,7 @@
         <v>43616</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C66"/>
       <c r="D66"/>
@@ -2709,7 +2535,7 @@
       <c r="F66"/>
       <c r="G66"/>
       <c r="H66" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I66"/>
       <c r="J66"/>
@@ -2720,7 +2546,7 @@
         <v>43616</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C67"/>
       <c r="D67"/>
@@ -2728,7 +2554,7 @@
       <c r="F67"/>
       <c r="G67"/>
       <c r="H67" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I67"/>
       <c r="J67"/>
@@ -2739,7 +2565,7 @@
         <v>43616</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C68"/>
       <c r="D68"/>
@@ -2747,7 +2573,7 @@
       <c r="F68"/>
       <c r="G68"/>
       <c r="H68" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="I68"/>
       <c r="J68"/>
@@ -2758,7 +2584,7 @@
         <v>43616</v>
       </c>
       <c r="B69" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C69"/>
       <c r="D69"/>
@@ -2777,7 +2603,7 @@
         <v>43646</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C70"/>
       <c r="D70"/>
@@ -2796,7 +2622,7 @@
         <v>43646</v>
       </c>
       <c r="B71" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C71"/>
       <c r="D71"/>
@@ -2823,7 +2649,7 @@
       <c r="F72"/>
       <c r="G72"/>
       <c r="H72" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="I72"/>
       <c r="J72"/>
@@ -2842,7 +2668,7 @@
       <c r="F73"/>
       <c r="G73"/>
       <c r="H73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I73"/>
       <c r="J73"/>
@@ -2853,7 +2679,7 @@
         <v>43677</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C74"/>
       <c r="D74"/>
@@ -2861,7 +2687,7 @@
       <c r="F74"/>
       <c r="G74"/>
       <c r="H74" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I74"/>
       <c r="J74"/>
@@ -2872,7 +2698,7 @@
         <v>43677</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C75"/>
       <c r="D75"/>
@@ -2880,7 +2706,7 @@
       <c r="F75"/>
       <c r="G75"/>
       <c r="H75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I75"/>
       <c r="J75"/>
@@ -2891,7 +2717,7 @@
         <v>43677</v>
       </c>
       <c r="B76" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C76"/>
       <c r="D76"/>
@@ -2899,7 +2725,7 @@
       <c r="F76"/>
       <c r="G76"/>
       <c r="H76" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I76"/>
       <c r="J76"/>
@@ -2918,7 +2744,7 @@
       <c r="F77"/>
       <c r="G77"/>
       <c r="H77" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I77"/>
       <c r="J77"/>
@@ -2929,7 +2755,7 @@
         <v>43708</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C78"/>
       <c r="D78"/>
@@ -2937,7 +2763,7 @@
       <c r="F78"/>
       <c r="G78"/>
       <c r="H78" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I78"/>
       <c r="J78"/>
@@ -2956,7 +2782,7 @@
       <c r="F79"/>
       <c r="G79"/>
       <c r="H79" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I79"/>
       <c r="J79"/>
@@ -2967,7 +2793,7 @@
         <v>43708</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C80"/>
       <c r="D80"/>
@@ -2975,7 +2801,7 @@
       <c r="F80"/>
       <c r="G80"/>
       <c r="H80" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I80"/>
       <c r="J80"/>
@@ -2986,7 +2812,7 @@
         <v>43708</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C81"/>
       <c r="D81"/>
@@ -2994,7 +2820,7 @@
       <c r="F81"/>
       <c r="G81"/>
       <c r="H81" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="I81"/>
       <c r="J81"/>
@@ -3005,7 +2831,7 @@
         <v>43738</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C82"/>
       <c r="D82"/>
@@ -3024,7 +2850,7 @@
         <v>43738</v>
       </c>
       <c r="B83" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C83"/>
       <c r="D83"/>
@@ -3043,7 +2869,7 @@
         <v>43738</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C84"/>
       <c r="D84"/>
@@ -3119,7 +2945,7 @@
         <v>43769</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C88"/>
       <c r="D88"/>
@@ -3138,7 +2964,7 @@
         <v>43769</v>
       </c>
       <c r="B89" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C89"/>
       <c r="D89"/>
@@ -3146,7 +2972,7 @@
       <c r="F89"/>
       <c r="G89"/>
       <c r="H89" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="I89"/>
       <c r="J89"/>
@@ -3157,7 +2983,7 @@
         <v>43799</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C90"/>
       <c r="D90"/>
@@ -3165,7 +2991,7 @@
       <c r="F90"/>
       <c r="G90"/>
       <c r="H90" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I90"/>
       <c r="J90"/>
@@ -3176,7 +3002,7 @@
         <v>43799</v>
       </c>
       <c r="B91" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C91"/>
       <c r="D91"/>
@@ -3184,7 +3010,7 @@
       <c r="F91"/>
       <c r="G91"/>
       <c r="H91" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I91"/>
       <c r="J91"/>
@@ -3195,7 +3021,7 @@
         <v>43799</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C92"/>
       <c r="D92"/>
@@ -3203,7 +3029,7 @@
       <c r="F92"/>
       <c r="G92"/>
       <c r="H92" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="I92"/>
       <c r="J92"/>
@@ -3214,7 +3040,7 @@
         <v>43799</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C93"/>
       <c r="D93"/>
@@ -3233,7 +3059,7 @@
         <v>43830</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C94"/>
       <c r="D94"/>
@@ -3252,7 +3078,7 @@
         <v>43830</v>
       </c>
       <c r="B95" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C95"/>
       <c r="D95"/>
@@ -3260,7 +3086,7 @@
       <c r="F95"/>
       <c r="G95"/>
       <c r="H95" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="I95"/>
       <c r="J95"/>
@@ -3271,7 +3097,7 @@
         <v>43830</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C96"/>
       <c r="D96"/>
@@ -3279,7 +3105,7 @@
       <c r="F96"/>
       <c r="G96"/>
       <c r="H96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I96"/>
       <c r="J96"/>
@@ -3290,7 +3116,7 @@
         <v>43830</v>
       </c>
       <c r="B97" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C97"/>
       <c r="D97"/>
@@ -3298,7 +3124,7 @@
       <c r="F97"/>
       <c r="G97"/>
       <c r="H97" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="I97"/>
       <c r="J97"/>
@@ -3317,7 +3143,7 @@
       <c r="F98"/>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I98"/>
       <c r="J98"/>
@@ -3328,7 +3154,7 @@
         <v>43861</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C99"/>
       <c r="D99"/>
@@ -3336,7 +3162,7 @@
       <c r="F99"/>
       <c r="G99"/>
       <c r="H99" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I99"/>
       <c r="J99"/>
@@ -3347,7 +3173,7 @@
         <v>43861</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C100"/>
       <c r="D100"/>
@@ -3355,7 +3181,7 @@
       <c r="F100"/>
       <c r="G100"/>
       <c r="H100" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I100"/>
       <c r="J100"/>
@@ -3366,7 +3192,7 @@
         <v>43861</v>
       </c>
       <c r="B101" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C101"/>
       <c r="D101"/>
@@ -3374,7 +3200,7 @@
       <c r="F101"/>
       <c r="G101"/>
       <c r="H101" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I101"/>
       <c r="J101"/>
@@ -3385,7 +3211,7 @@
         <v>43890</v>
       </c>
       <c r="B102" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C102"/>
       <c r="D102"/>
@@ -3393,7 +3219,7 @@
       <c r="F102"/>
       <c r="G102"/>
       <c r="H102" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I102"/>
       <c r="J102"/>
@@ -3404,7 +3230,7 @@
         <v>43890</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C103"/>
       <c r="D103"/>
@@ -3412,7 +3238,7 @@
       <c r="F103"/>
       <c r="G103"/>
       <c r="H103" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="I103"/>
       <c r="J103"/>
@@ -3423,7 +3249,7 @@
         <v>43890</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C104"/>
       <c r="D104"/>
@@ -3431,7 +3257,7 @@
       <c r="F104"/>
       <c r="G104"/>
       <c r="H104" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I104"/>
       <c r="J104"/>
@@ -3450,7 +3276,7 @@
       <c r="F105"/>
       <c r="G105"/>
       <c r="H105" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I105"/>
       <c r="J105"/>
@@ -3461,7 +3287,7 @@
         <v>43921</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C106"/>
       <c r="D106"/>
@@ -3469,7 +3295,7 @@
       <c r="F106"/>
       <c r="G106"/>
       <c r="H106" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="I106"/>
       <c r="J106"/>
@@ -3488,7 +3314,7 @@
       <c r="F107"/>
       <c r="G107"/>
       <c r="H107" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I107"/>
       <c r="J107"/>
@@ -3499,7 +3325,7 @@
         <v>43921</v>
       </c>
       <c r="B108" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C108"/>
       <c r="D108"/>
@@ -3507,7 +3333,7 @@
       <c r="F108"/>
       <c r="G108"/>
       <c r="H108" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I108"/>
       <c r="J108"/>
@@ -3518,7 +3344,7 @@
         <v>43921</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C109"/>
       <c r="D109"/>
@@ -3526,7 +3352,7 @@
       <c r="F109"/>
       <c r="G109"/>
       <c r="H109" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I109"/>
       <c r="J109"/>
@@ -3537,7 +3363,7 @@
         <v>43951</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C110"/>
       <c r="D110"/>
@@ -3545,7 +3371,7 @@
       <c r="F110"/>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I110"/>
       <c r="J110"/>
@@ -3556,7 +3382,7 @@
         <v>43951</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C111"/>
       <c r="D111"/>
@@ -3564,7 +3390,7 @@
       <c r="F111"/>
       <c r="G111"/>
       <c r="H111" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="I111"/>
       <c r="J111"/>
@@ -3575,7 +3401,7 @@
         <v>43951</v>
       </c>
       <c r="B112" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C112"/>
       <c r="D112"/>
@@ -3583,7 +3409,7 @@
       <c r="F112"/>
       <c r="G112"/>
       <c r="H112" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="I112"/>
       <c r="J112"/>
@@ -3594,7 +3420,7 @@
         <v>43951</v>
       </c>
       <c r="B113" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C113"/>
       <c r="D113"/>
@@ -3602,7 +3428,7 @@
       <c r="F113"/>
       <c r="G113"/>
       <c r="H113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I113"/>
       <c r="J113"/>
@@ -3621,7 +3447,7 @@
       <c r="F114"/>
       <c r="G114"/>
       <c r="H114" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I114"/>
       <c r="J114"/>
@@ -3640,7 +3466,7 @@
       <c r="F115"/>
       <c r="G115"/>
       <c r="H115" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I115"/>
       <c r="J115"/>
@@ -3651,7 +3477,7 @@
         <v>43982</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C116"/>
       <c r="D116"/>
@@ -3659,7 +3485,7 @@
       <c r="F116"/>
       <c r="G116"/>
       <c r="H116" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="I116"/>
       <c r="J116"/>
@@ -3670,7 +3496,7 @@
         <v>43982</v>
       </c>
       <c r="B117" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C117"/>
       <c r="D117"/>
@@ -3697,7 +3523,7 @@
       <c r="F118"/>
       <c r="G118"/>
       <c r="H118" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="I118"/>
       <c r="J118"/>
@@ -3708,7 +3534,7 @@
         <v>44012</v>
       </c>
       <c r="B119" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C119"/>
       <c r="D119"/>
@@ -3716,7 +3542,7 @@
       <c r="F119"/>
       <c r="G119"/>
       <c r="H119" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I119"/>
       <c r="J119"/>
@@ -3727,7 +3553,7 @@
         <v>44012</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C120"/>
       <c r="D120"/>
@@ -3735,7 +3561,7 @@
       <c r="F120"/>
       <c r="G120"/>
       <c r="H120" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I120"/>
       <c r="J120"/>
@@ -3746,7 +3572,7 @@
         <v>44012</v>
       </c>
       <c r="B121" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C121"/>
       <c r="D121"/>
@@ -3754,7 +3580,7 @@
       <c r="F121"/>
       <c r="G121"/>
       <c r="H121" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I121"/>
       <c r="J121"/>
@@ -3765,7 +3591,7 @@
         <v>44043</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C122"/>
       <c r="D122"/>
@@ -3773,7 +3599,7 @@
       <c r="F122"/>
       <c r="G122"/>
       <c r="H122" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I122"/>
       <c r="J122"/>
@@ -3792,7 +3618,7 @@
       <c r="F123"/>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I123"/>
       <c r="J123"/>
@@ -3803,7 +3629,7 @@
         <v>44043</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C124"/>
       <c r="D124"/>
@@ -3811,7 +3637,7 @@
       <c r="F124"/>
       <c r="G124"/>
       <c r="H124" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="I124"/>
       <c r="J124"/>
@@ -3830,7 +3656,7 @@
       <c r="F125"/>
       <c r="G125"/>
       <c r="H125" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="I125"/>
       <c r="J125"/>
@@ -3849,7 +3675,7 @@
       <c r="F126"/>
       <c r="G126"/>
       <c r="H126" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I126"/>
       <c r="J126"/>
@@ -3868,7 +3694,7 @@
       <c r="F127"/>
       <c r="G127"/>
       <c r="H127" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="I127"/>
       <c r="J127"/>
@@ -3879,7 +3705,7 @@
         <v>44074</v>
       </c>
       <c r="B128" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C128"/>
       <c r="D128"/>
@@ -3887,7 +3713,7 @@
       <c r="F128"/>
       <c r="G128"/>
       <c r="H128" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I128"/>
       <c r="J128"/>
@@ -3898,7 +3724,7 @@
         <v>44074</v>
       </c>
       <c r="B129" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C129"/>
       <c r="D129"/>
@@ -3906,7 +3732,7 @@
       <c r="F129"/>
       <c r="G129"/>
       <c r="H129" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I129"/>
       <c r="J129"/>
@@ -3917,7 +3743,7 @@
         <v>44104</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C130"/>
       <c r="D130"/>
@@ -3925,7 +3751,7 @@
       <c r="F130"/>
       <c r="G130"/>
       <c r="H130" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I130"/>
       <c r="J130"/>
@@ -3944,7 +3770,7 @@
       <c r="F131"/>
       <c r="G131"/>
       <c r="H131" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="I131"/>
       <c r="J131"/>
@@ -3955,7 +3781,7 @@
         <v>44104</v>
       </c>
       <c r="B132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C132"/>
       <c r="D132"/>
@@ -3963,7 +3789,7 @@
       <c r="F132"/>
       <c r="G132"/>
       <c r="H132" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I132"/>
       <c r="J132"/>
@@ -3982,7 +3808,7 @@
       <c r="F133"/>
       <c r="G133"/>
       <c r="H133" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I133"/>
       <c r="J133"/>
@@ -3993,7 +3819,7 @@
         <v>44135</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C134"/>
       <c r="D134"/>
@@ -4001,7 +3827,7 @@
       <c r="F134"/>
       <c r="G134"/>
       <c r="H134" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I134"/>
       <c r="J134"/>
@@ -4012,7 +3838,7 @@
         <v>44135</v>
       </c>
       <c r="B135" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C135"/>
       <c r="D135"/>
@@ -4020,7 +3846,7 @@
       <c r="F135"/>
       <c r="G135"/>
       <c r="H135" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I135"/>
       <c r="J135"/>
@@ -4031,7 +3857,7 @@
         <v>44135</v>
       </c>
       <c r="B136" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C136"/>
       <c r="D136"/>
@@ -4039,7 +3865,7 @@
       <c r="F136"/>
       <c r="G136"/>
       <c r="H136" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I136"/>
       <c r="J136"/>
@@ -4050,7 +3876,7 @@
         <v>44135</v>
       </c>
       <c r="B137" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C137"/>
       <c r="D137"/>
@@ -4058,7 +3884,7 @@
       <c r="F137"/>
       <c r="G137"/>
       <c r="H137" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="I137"/>
       <c r="J137"/>
@@ -4077,7 +3903,7 @@
       <c r="F138"/>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I138"/>
       <c r="J138"/>
@@ -4088,7 +3914,7 @@
         <v>44165</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C139"/>
       <c r="D139"/>
@@ -4096,7 +3922,7 @@
       <c r="F139"/>
       <c r="G139"/>
       <c r="H139" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="I139"/>
       <c r="J139"/>
@@ -4107,7 +3933,7 @@
         <v>44165</v>
       </c>
       <c r="B140" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C140"/>
       <c r="D140"/>
@@ -4115,7 +3941,7 @@
       <c r="F140"/>
       <c r="G140"/>
       <c r="H140" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I140"/>
       <c r="J140"/>
@@ -4126,7 +3952,7 @@
         <v>44165</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C141"/>
       <c r="D141"/>
@@ -4134,7 +3960,7 @@
       <c r="F141"/>
       <c r="G141"/>
       <c r="H141" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I141"/>
       <c r="J141"/>
@@ -4145,7 +3971,7 @@
         <v>44196</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C142"/>
       <c r="D142"/>
@@ -4153,7 +3979,7 @@
       <c r="F142"/>
       <c r="G142"/>
       <c r="H142" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I142"/>
       <c r="J142"/>
@@ -4164,7 +3990,7 @@
         <v>44196</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C143"/>
       <c r="D143"/>
@@ -4172,7 +3998,7 @@
       <c r="F143"/>
       <c r="G143"/>
       <c r="H143" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I143"/>
       <c r="J143"/>
@@ -4183,7 +4009,7 @@
         <v>44196</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C144"/>
       <c r="D144"/>
@@ -4191,7 +4017,7 @@
       <c r="F144"/>
       <c r="G144"/>
       <c r="H144" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I144"/>
       <c r="J144"/>
@@ -4210,7 +4036,7 @@
       <c r="F145"/>
       <c r="G145"/>
       <c r="H145" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I145"/>
       <c r="J145"/>
@@ -4221,7 +4047,7 @@
         <v>44227</v>
       </c>
       <c r="B146" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C146"/>
       <c r="D146"/>
@@ -4229,7 +4055,7 @@
       <c r="F146"/>
       <c r="G146"/>
       <c r="H146" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I146"/>
       <c r="J146"/>
@@ -4248,7 +4074,7 @@
       <c r="F147"/>
       <c r="G147"/>
       <c r="H147" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I147"/>
       <c r="J147"/>
@@ -4259,7 +4085,7 @@
         <v>44227</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C148"/>
       <c r="D148"/>
@@ -4267,7 +4093,7 @@
       <c r="F148"/>
       <c r="G148"/>
       <c r="H148" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="I148"/>
       <c r="J148"/>
@@ -4278,7 +4104,7 @@
         <v>44227</v>
       </c>
       <c r="B149" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C149"/>
       <c r="D149"/>
@@ -4286,7 +4112,7 @@
       <c r="F149"/>
       <c r="G149"/>
       <c r="H149" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I149"/>
       <c r="J149"/>
@@ -4297,7 +4123,7 @@
         <v>44255</v>
       </c>
       <c r="B150" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C150"/>
       <c r="D150"/>
@@ -4305,7 +4131,7 @@
       <c r="F150"/>
       <c r="G150"/>
       <c r="H150" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I150"/>
       <c r="J150"/>
@@ -4316,7 +4142,7 @@
         <v>44255</v>
       </c>
       <c r="B151" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C151"/>
       <c r="D151"/>
@@ -4324,7 +4150,7 @@
       <c r="F151"/>
       <c r="G151"/>
       <c r="H151" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I151"/>
       <c r="J151"/>
@@ -4343,7 +4169,7 @@
       <c r="F152"/>
       <c r="G152"/>
       <c r="H152" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I152"/>
       <c r="J152"/>
@@ -4354,7 +4180,7 @@
         <v>44255</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C153"/>
       <c r="D153"/>
@@ -4362,7 +4188,7 @@
       <c r="F153"/>
       <c r="G153"/>
       <c r="H153" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I153"/>
       <c r="J153"/>
@@ -4373,7 +4199,7 @@
         <v>44286</v>
       </c>
       <c r="B154" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C154"/>
       <c r="D154"/>
@@ -4381,7 +4207,7 @@
       <c r="F154"/>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I154"/>
       <c r="J154"/>
@@ -4400,7 +4226,7 @@
       <c r="F155"/>
       <c r="G155"/>
       <c r="H155" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="I155"/>
       <c r="J155"/>
@@ -4411,7 +4237,7 @@
         <v>44286</v>
       </c>
       <c r="B156" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C156"/>
       <c r="D156"/>
@@ -4419,7 +4245,7 @@
       <c r="F156"/>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I156"/>
       <c r="J156"/>
@@ -4438,7 +4264,7 @@
       <c r="F157"/>
       <c r="G157"/>
       <c r="H157" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I157"/>
       <c r="J157"/>
@@ -4457,7 +4283,7 @@
       <c r="F158"/>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I158"/>
       <c r="J158"/>
@@ -4468,7 +4294,7 @@
         <v>44316</v>
       </c>
       <c r="B159" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C159"/>
       <c r="D159"/>
@@ -4476,7 +4302,7 @@
       <c r="F159"/>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="I159"/>
       <c r="J159"/>
@@ -4487,7 +4313,7 @@
         <v>44316</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C160"/>
       <c r="D160"/>
@@ -4495,7 +4321,7 @@
       <c r="F160"/>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I160"/>
       <c r="J160"/>
@@ -4506,7 +4332,7 @@
         <v>44316</v>
       </c>
       <c r="B161" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C161"/>
       <c r="D161"/>
@@ -4514,7 +4340,7 @@
       <c r="F161"/>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I161"/>
       <c r="J161"/>
@@ -4525,7 +4351,7 @@
         <v>44347</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
@@ -4533,7 +4359,7 @@
       <c r="F162"/>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I162"/>
       <c r="J162"/>
@@ -4544,7 +4370,7 @@
         <v>44347</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
@@ -4552,7 +4378,7 @@
       <c r="F163"/>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I163"/>
       <c r="J163"/>
@@ -4571,7 +4397,7 @@
       <c r="F164"/>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="I164"/>
       <c r="J164"/>
@@ -4590,7 +4416,7 @@
       <c r="F165"/>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I165"/>
       <c r="J165"/>
@@ -4601,7 +4427,7 @@
         <v>44377</v>
       </c>
       <c r="B166" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C166"/>
       <c r="D166"/>
@@ -4609,7 +4435,7 @@
       <c r="F166"/>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I166"/>
       <c r="J166"/>
@@ -4628,7 +4454,7 @@
       <c r="F167"/>
       <c r="G167"/>
       <c r="H167" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
       <c r="I167"/>
       <c r="J167"/>
@@ -4639,7 +4465,7 @@
         <v>44377</v>
       </c>
       <c r="B168" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C168"/>
       <c r="D168"/>
@@ -4647,7 +4473,7 @@
       <c r="F168"/>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="I168"/>
       <c r="J168"/>
@@ -4658,7 +4484,7 @@
         <v>44377</v>
       </c>
       <c r="B169" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
@@ -4666,7 +4492,7 @@
       <c r="F169"/>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I169"/>
       <c r="J169"/>
@@ -4677,7 +4503,7 @@
         <v>44408</v>
       </c>
       <c r="B170" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
@@ -4685,7 +4511,7 @@
       <c r="F170"/>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I170"/>
       <c r="J170"/>
@@ -4696,7 +4522,7 @@
         <v>44408</v>
       </c>
       <c r="B171" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
@@ -4704,7 +4530,7 @@
       <c r="F171"/>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="I171"/>
       <c r="J171"/>
@@ -4715,7 +4541,7 @@
         <v>44408</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
@@ -4723,7 +4549,7 @@
       <c r="F172"/>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="I172"/>
       <c r="J172"/>
@@ -4742,7 +4568,7 @@
       <c r="F173"/>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="I173"/>
       <c r="J173"/>
@@ -4761,7 +4587,7 @@
       <c r="F174"/>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="I174"/>
       <c r="J174"/>
@@ -4780,7 +4606,7 @@
       <c r="F175"/>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="I175"/>
       <c r="J175"/>
@@ -4799,7 +4625,7 @@
       <c r="F176"/>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="I176"/>
       <c r="J176"/>
@@ -4818,7 +4644,7 @@
       <c r="F177"/>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="I177"/>
       <c r="J177"/>
@@ -4829,7 +4655,7 @@
         <v>44469</v>
       </c>
       <c r="B178" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
@@ -4837,7 +4663,7 @@
       <c r="F178"/>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="I178"/>
       <c r="J178"/>
@@ -4848,7 +4674,7 @@
         <v>44469</v>
       </c>
       <c r="B179" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C179"/>
       <c r="D179"/>
@@ -4856,7 +4682,7 @@
       <c r="F179"/>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I179"/>
       <c r="J179"/>
@@ -4867,7 +4693,7 @@
         <v>44469</v>
       </c>
       <c r="B180" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
@@ -4875,7 +4701,7 @@
       <c r="F180"/>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="I180"/>
       <c r="J180"/>
@@ -4886,7 +4712,7 @@
         <v>44469</v>
       </c>
       <c r="B181" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
@@ -4894,7 +4720,7 @@
       <c r="F181"/>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="I181"/>
       <c r="J181"/>
@@ -4913,7 +4739,7 @@
       <c r="F182"/>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="I182"/>
       <c r="J182"/>
@@ -4924,7 +4750,7 @@
         <v>44500</v>
       </c>
       <c r="B183" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
@@ -4932,7 +4758,7 @@
       <c r="F183"/>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="I183"/>
       <c r="J183"/>
@@ -4943,7 +4769,7 @@
         <v>44500</v>
       </c>
       <c r="B184" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C184"/>
       <c r="D184"/>
@@ -4951,7 +4777,7 @@
       <c r="F184"/>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="I184"/>
       <c r="J184"/>
@@ -4962,7 +4788,7 @@
         <v>44500</v>
       </c>
       <c r="B185" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
@@ -4970,7 +4796,7 @@
       <c r="F185"/>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I185"/>
       <c r="J185"/>
@@ -4989,7 +4815,7 @@
       <c r="F186"/>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I186"/>
       <c r="J186"/>
@@ -5008,7 +4834,7 @@
       <c r="F187"/>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="I187"/>
       <c r="J187"/>
@@ -5019,7 +4845,7 @@
         <v>44530</v>
       </c>
       <c r="B188" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C188"/>
       <c r="D188"/>
@@ -5027,7 +4853,7 @@
       <c r="F188"/>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="I188"/>
       <c r="J188"/>
@@ -5038,7 +4864,7 @@
         <v>44530</v>
       </c>
       <c r="B189" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
@@ -5046,7 +4872,7 @@
       <c r="F189"/>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="I189"/>
       <c r="J189"/>
@@ -5065,7 +4891,7 @@
       <c r="F190"/>
       <c r="G190"/>
       <c r="H190" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="I190"/>
       <c r="J190"/>
@@ -5076,7 +4902,7 @@
         <v>44561</v>
       </c>
       <c r="B191" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C191"/>
       <c r="D191"/>
@@ -5084,7 +4910,7 @@
       <c r="F191"/>
       <c r="G191"/>
       <c r="H191" t="s">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="I191"/>
       <c r="J191"/>
@@ -5103,7 +4929,7 @@
       <c r="F192"/>
       <c r="G192"/>
       <c r="H192" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="I192"/>
       <c r="J192"/>
@@ -5114,7 +4940,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C193"/>
       <c r="D193"/>
@@ -5122,7 +4948,7 @@
       <c r="F193"/>
       <c r="G193"/>
       <c r="H193" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="I193"/>
       <c r="J193"/>
@@ -5133,7 +4959,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C194"/>
       <c r="D194"/>
@@ -5141,7 +4967,7 @@
       <c r="F194"/>
       <c r="G194"/>
       <c r="H194" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="I194"/>
       <c r="J194"/>
@@ -5152,7 +4978,7 @@
         <v>44592</v>
       </c>
       <c r="B195" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C195"/>
       <c r="D195"/>
@@ -5160,7 +4986,7 @@
       <c r="F195"/>
       <c r="G195"/>
       <c r="H195" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="I195"/>
       <c r="J195"/>
@@ -5171,7 +4997,7 @@
         <v>44592</v>
       </c>
       <c r="B196" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C196"/>
       <c r="D196"/>
@@ -5179,7 +5005,7 @@
       <c r="F196"/>
       <c r="G196"/>
       <c r="H196" t="s">
-        <v>192</v>
+        <v>75</v>
       </c>
       <c r="I196"/>
       <c r="J196"/>
@@ -5198,7 +5024,7 @@
       <c r="F197"/>
       <c r="G197"/>
       <c r="H197" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I197"/>
       <c r="J197"/>
@@ -5209,7 +5035,7 @@
         <v>44620</v>
       </c>
       <c r="B198" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C198"/>
       <c r="D198"/>
@@ -5217,7 +5043,7 @@
       <c r="F198"/>
       <c r="G198"/>
       <c r="H198" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="I198"/>
       <c r="J198"/>
@@ -5228,7 +5054,7 @@
         <v>44620</v>
       </c>
       <c r="B199" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C199"/>
       <c r="D199"/>
@@ -5236,7 +5062,7 @@
       <c r="F199"/>
       <c r="G199"/>
       <c r="H199" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="I199"/>
       <c r="J199"/>
@@ -5247,7 +5073,7 @@
         <v>44620</v>
       </c>
       <c r="B200" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C200"/>
       <c r="D200"/>
@@ -5255,7 +5081,7 @@
       <c r="F200"/>
       <c r="G200"/>
       <c r="H200" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="I200"/>
       <c r="J200"/>
@@ -5274,7 +5100,7 @@
       <c r="F201"/>
       <c r="G201"/>
       <c r="H201" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="I201"/>
       <c r="J201"/>
@@ -5285,7 +5111,7 @@
         <v>44651</v>
       </c>
       <c r="B202" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C202"/>
       <c r="D202"/>
@@ -5293,7 +5119,7 @@
       <c r="F202"/>
       <c r="G202"/>
       <c r="H202" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="I202"/>
       <c r="J202"/>
@@ -5304,7 +5130,7 @@
         <v>44651</v>
       </c>
       <c r="B203" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C203"/>
       <c r="D203"/>
@@ -5312,7 +5138,7 @@
       <c r="F203"/>
       <c r="G203"/>
       <c r="H203" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="I203"/>
       <c r="J203"/>
@@ -5323,7 +5149,7 @@
         <v>44651</v>
       </c>
       <c r="B204" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C204"/>
       <c r="D204"/>
@@ -5331,7 +5157,7 @@
       <c r="F204"/>
       <c r="G204"/>
       <c r="H204" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="I204"/>
       <c r="J204"/>
@@ -5342,7 +5168,7 @@
         <v>44651</v>
       </c>
       <c r="B205" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C205"/>
       <c r="D205"/>
@@ -5350,7 +5176,7 @@
       <c r="F205"/>
       <c r="G205"/>
       <c r="H205" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="I205"/>
       <c r="J205"/>
@@ -5361,7 +5187,7 @@
         <v>44681</v>
       </c>
       <c r="B206" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C206"/>
       <c r="D206"/>
@@ -5369,7 +5195,7 @@
       <c r="F206"/>
       <c r="G206"/>
       <c r="H206" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="I206"/>
       <c r="J206"/>
@@ -5380,7 +5206,7 @@
         <v>44681</v>
       </c>
       <c r="B207" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C207"/>
       <c r="D207"/>
@@ -5388,7 +5214,7 @@
       <c r="F207"/>
       <c r="G207"/>
       <c r="H207" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="I207"/>
       <c r="J207"/>
@@ -5399,7 +5225,7 @@
         <v>44681</v>
       </c>
       <c r="B208" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C208"/>
       <c r="D208"/>
@@ -5407,7 +5233,7 @@
       <c r="F208"/>
       <c r="G208"/>
       <c r="H208" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="I208"/>
       <c r="J208"/>
@@ -5418,7 +5244,7 @@
         <v>44681</v>
       </c>
       <c r="B209" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C209"/>
       <c r="D209"/>
@@ -5426,7 +5252,7 @@
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="I209"/>
       <c r="J209"/>
@@ -5437,7 +5263,7 @@
         <v>44712</v>
       </c>
       <c r="B210" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C210"/>
       <c r="D210"/>
@@ -5445,7 +5271,7 @@
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="I210"/>
       <c r="J210"/>
@@ -5464,7 +5290,7 @@
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="I211"/>
       <c r="J211"/>
@@ -5483,7 +5309,7 @@
       <c r="F212"/>
       <c r="G212"/>
       <c r="H212" t="s">
-        <v>208</v>
+        <v>109</v>
       </c>
       <c r="I212"/>
       <c r="J212"/>
@@ -5494,7 +5320,7 @@
         <v>44712</v>
       </c>
       <c r="B213" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C213"/>
       <c r="D213"/>
@@ -5502,7 +5328,7 @@
       <c r="F213"/>
       <c r="G213"/>
       <c r="H213" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
       <c r="I213"/>
       <c r="J213"/>
@@ -5513,7 +5339,7 @@
         <v>44742</v>
       </c>
       <c r="B214" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C214"/>
       <c r="D214"/>
@@ -5521,7 +5347,7 @@
       <c r="F214"/>
       <c r="G214"/>
       <c r="H214" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="I214"/>
       <c r="J214"/>
@@ -5532,7 +5358,7 @@
         <v>44742</v>
       </c>
       <c r="B215" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C215"/>
       <c r="D215"/>
@@ -5540,7 +5366,7 @@
       <c r="F215"/>
       <c r="G215"/>
       <c r="H215" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I215"/>
       <c r="J215"/>
@@ -5559,7 +5385,7 @@
       <c r="F216"/>
       <c r="G216"/>
       <c r="H216" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="I216"/>
       <c r="J216"/>
@@ -5570,7 +5396,7 @@
         <v>44742</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C217"/>
       <c r="D217"/>
@@ -5578,7 +5404,7 @@
       <c r="F217"/>
       <c r="G217"/>
       <c r="H217" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="I217"/>
       <c r="J217"/>
@@ -5597,7 +5423,7 @@
       <c r="F218"/>
       <c r="G218"/>
       <c r="H218" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="I218"/>
       <c r="J218"/>
@@ -5616,7 +5442,7 @@
       <c r="F219"/>
       <c r="G219"/>
       <c r="H219" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I219"/>
       <c r="J219"/>
@@ -5635,7 +5461,7 @@
       <c r="F220"/>
       <c r="G220"/>
       <c r="H220" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="I220"/>
       <c r="J220"/>
@@ -5654,7 +5480,7 @@
       <c r="F221"/>
       <c r="G221"/>
       <c r="H221" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="I221"/>
       <c r="J221"/>
@@ -5673,7 +5499,7 @@
       <c r="F222"/>
       <c r="G222"/>
       <c r="H222" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="I222"/>
       <c r="J222"/>
@@ -5692,7 +5518,7 @@
       <c r="F223"/>
       <c r="G223"/>
       <c r="H223" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="I223"/>
       <c r="J223"/>
@@ -5703,7 +5529,7 @@
         <v>44804</v>
       </c>
       <c r="B224" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C224"/>
       <c r="D224"/>
@@ -5711,7 +5537,7 @@
       <c r="F224"/>
       <c r="G224"/>
       <c r="H224" t="s">
-        <v>68</v>
+        <v>204</v>
       </c>
       <c r="I224"/>
       <c r="J224"/>
@@ -5722,7 +5548,7 @@
         <v>44804</v>
       </c>
       <c r="B225" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C225"/>
       <c r="D225"/>
@@ -5730,7 +5556,7 @@
       <c r="F225"/>
       <c r="G225"/>
       <c r="H225" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="I225"/>
       <c r="J225"/>
@@ -5741,7 +5567,7 @@
         <v>44834</v>
       </c>
       <c r="B226" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C226"/>
       <c r="D226"/>
@@ -5749,7 +5575,7 @@
       <c r="F226"/>
       <c r="G226"/>
       <c r="H226" t="s">
-        <v>219</v>
+        <v>95</v>
       </c>
       <c r="I226"/>
       <c r="J226"/>
@@ -5760,7 +5586,7 @@
         <v>44834</v>
       </c>
       <c r="B227" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C227"/>
       <c r="D227"/>
@@ -5768,7 +5594,7 @@
       <c r="F227"/>
       <c r="G227"/>
       <c r="H227" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="I227"/>
       <c r="J227"/>
@@ -5779,7 +5605,7 @@
         <v>44834</v>
       </c>
       <c r="B228" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C228"/>
       <c r="D228"/>
@@ -5787,7 +5613,7 @@
       <c r="F228"/>
       <c r="G228"/>
       <c r="H228" t="s">
-        <v>220</v>
+        <v>52</v>
       </c>
       <c r="I228"/>
       <c r="J228"/>
@@ -5798,7 +5624,7 @@
         <v>44834</v>
       </c>
       <c r="B229" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C229"/>
       <c r="D229"/>
@@ -5806,7 +5632,7 @@
       <c r="F229"/>
       <c r="G229"/>
       <c r="H229" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="I229"/>
       <c r="J229"/>
@@ -5825,7 +5651,7 @@
       <c r="F230"/>
       <c r="G230"/>
       <c r="H230" t="s">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="I230"/>
       <c r="J230"/>
@@ -5836,7 +5662,7 @@
         <v>44865</v>
       </c>
       <c r="B231" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C231"/>
       <c r="D231"/>
@@ -5844,7 +5670,7 @@
       <c r="F231"/>
       <c r="G231"/>
       <c r="H231" t="s">
-        <v>222</v>
+        <v>161</v>
       </c>
       <c r="I231"/>
       <c r="J231"/>
@@ -5855,7 +5681,7 @@
         <v>44865</v>
       </c>
       <c r="B232" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C232"/>
       <c r="D232"/>
@@ -5863,7 +5689,7 @@
       <c r="F232"/>
       <c r="G232"/>
       <c r="H232" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="I232"/>
       <c r="J232"/>
@@ -5874,7 +5700,7 @@
         <v>44865</v>
       </c>
       <c r="B233" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C233"/>
       <c r="D233"/>
@@ -5882,7 +5708,7 @@
       <c r="F233"/>
       <c r="G233"/>
       <c r="H233" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="I233"/>
       <c r="J233"/>
@@ -5893,7 +5719,7 @@
         <v>44895</v>
       </c>
       <c r="B234" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C234"/>
       <c r="D234"/>
@@ -5901,7 +5727,7 @@
       <c r="F234"/>
       <c r="G234"/>
       <c r="H234" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="I234"/>
       <c r="J234"/>
@@ -5912,7 +5738,7 @@
         <v>44895</v>
       </c>
       <c r="B235" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C235"/>
       <c r="D235"/>
@@ -5920,7 +5746,7 @@
       <c r="F235"/>
       <c r="G235"/>
       <c r="H235" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="I235"/>
       <c r="J235"/>
@@ -5931,7 +5757,7 @@
         <v>44895</v>
       </c>
       <c r="B236" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C236"/>
       <c r="D236"/>
@@ -5939,7 +5765,7 @@
       <c r="F236"/>
       <c r="G236"/>
       <c r="H236" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="I236"/>
       <c r="J236"/>
@@ -5950,7 +5776,7 @@
         <v>44895</v>
       </c>
       <c r="B237" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C237"/>
       <c r="D237"/>
@@ -5958,7 +5784,7 @@
       <c r="F237"/>
       <c r="G237"/>
       <c r="H237" t="s">
-        <v>38</v>
+        <v>209</v>
       </c>
       <c r="I237"/>
       <c r="J237"/>
@@ -5969,7 +5795,7 @@
         <v>44926</v>
       </c>
       <c r="B238" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C238"/>
       <c r="D238"/>
@@ -5977,7 +5803,7 @@
       <c r="F238"/>
       <c r="G238"/>
       <c r="H238" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="I238"/>
       <c r="J238"/>
@@ -5988,7 +5814,7 @@
         <v>44926</v>
       </c>
       <c r="B239" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C239"/>
       <c r="D239"/>
@@ -5996,7 +5822,7 @@
       <c r="F239"/>
       <c r="G239"/>
       <c r="H239" t="s">
-        <v>229</v>
+        <v>103</v>
       </c>
       <c r="I239"/>
       <c r="J239"/>
@@ -6007,7 +5833,7 @@
         <v>44926</v>
       </c>
       <c r="B240" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C240"/>
       <c r="D240"/>
@@ -6015,7 +5841,7 @@
       <c r="F240"/>
       <c r="G240"/>
       <c r="H240" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="I240"/>
       <c r="J240"/>
@@ -6026,7 +5852,7 @@
         <v>44926</v>
       </c>
       <c r="B241" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C241"/>
       <c r="D241"/>
@@ -6034,7 +5860,7 @@
       <c r="F241"/>
       <c r="G241"/>
       <c r="H241" t="s">
-        <v>40</v>
+        <v>214</v>
       </c>
       <c r="I241"/>
       <c r="J241"/>
@@ -6045,7 +5871,7 @@
         <v>44957</v>
       </c>
       <c r="B242" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C242"/>
       <c r="D242"/>
@@ -6053,7 +5879,7 @@
       <c r="F242"/>
       <c r="G242"/>
       <c r="H242" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="I242"/>
       <c r="J242"/>
@@ -6064,7 +5890,7 @@
         <v>44957</v>
       </c>
       <c r="B243" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C243"/>
       <c r="D243"/>
@@ -6072,7 +5898,7 @@
       <c r="F243"/>
       <c r="G243"/>
       <c r="H243" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="I243"/>
       <c r="J243"/>
@@ -6083,7 +5909,7 @@
         <v>44957</v>
       </c>
       <c r="B244" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C244"/>
       <c r="D244"/>
@@ -6091,7 +5917,7 @@
       <c r="F244"/>
       <c r="G244"/>
       <c r="H244" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="I244"/>
       <c r="J244"/>
@@ -6102,7 +5928,7 @@
         <v>44957</v>
       </c>
       <c r="B245" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C245"/>
       <c r="D245"/>
@@ -6110,7 +5936,7 @@
       <c r="F245"/>
       <c r="G245"/>
       <c r="H245" t="s">
-        <v>234</v>
+        <v>108</v>
       </c>
       <c r="I245"/>
       <c r="J245"/>
@@ -6121,7 +5947,7 @@
         <v>44985</v>
       </c>
       <c r="B246" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C246"/>
       <c r="D246"/>
@@ -6129,7 +5955,7 @@
       <c r="F246"/>
       <c r="G246"/>
       <c r="H246" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="I246"/>
       <c r="J246"/>
@@ -6140,7 +5966,7 @@
         <v>44985</v>
       </c>
       <c r="B247" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C247"/>
       <c r="D247"/>
@@ -6148,7 +5974,7 @@
       <c r="F247"/>
       <c r="G247"/>
       <c r="H247" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="I247"/>
       <c r="J247"/>
@@ -6159,7 +5985,7 @@
         <v>44985</v>
       </c>
       <c r="B248" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C248"/>
       <c r="D248"/>
@@ -6167,7 +5993,7 @@
       <c r="F248"/>
       <c r="G248"/>
       <c r="H248" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="I248"/>
       <c r="J248"/>
@@ -6178,7 +6004,7 @@
         <v>44985</v>
       </c>
       <c r="B249" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C249"/>
       <c r="D249"/>
@@ -6186,7 +6012,7 @@
       <c r="F249"/>
       <c r="G249"/>
       <c r="H249" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="I249"/>
       <c r="J249"/>
@@ -6197,7 +6023,7 @@
         <v>45016</v>
       </c>
       <c r="B250" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C250"/>
       <c r="D250"/>
@@ -6205,7 +6031,7 @@
       <c r="F250"/>
       <c r="G250"/>
       <c r="H250" t="s">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="I250"/>
       <c r="J250"/>
@@ -6216,7 +6042,7 @@
         <v>45016</v>
       </c>
       <c r="B251" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C251"/>
       <c r="D251"/>
@@ -6224,7 +6050,7 @@
       <c r="F251"/>
       <c r="G251"/>
       <c r="H251" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I251"/>
       <c r="J251"/>
@@ -6235,7 +6061,7 @@
         <v>45016</v>
       </c>
       <c r="B252" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C252"/>
       <c r="D252"/>
@@ -6243,7 +6069,7 @@
       <c r="F252"/>
       <c r="G252"/>
       <c r="H252" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="I252"/>
       <c r="J252"/>
@@ -6254,7 +6080,7 @@
         <v>45016</v>
       </c>
       <c r="B253" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C253"/>
       <c r="D253"/>
@@ -6262,7 +6088,7 @@
       <c r="F253"/>
       <c r="G253"/>
       <c r="H253" t="s">
-        <v>240</v>
+        <v>186</v>
       </c>
       <c r="I253"/>
       <c r="J253"/>
@@ -6273,7 +6099,7 @@
         <v>45046</v>
       </c>
       <c r="B254" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C254"/>
       <c r="D254"/>
@@ -6281,7 +6107,7 @@
       <c r="F254"/>
       <c r="G254"/>
       <c r="H254" t="s">
-        <v>241</v>
+        <v>44</v>
       </c>
       <c r="I254"/>
       <c r="J254"/>
@@ -6292,7 +6118,7 @@
         <v>45046</v>
       </c>
       <c r="B255" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C255"/>
       <c r="D255"/>
@@ -6300,7 +6126,7 @@
       <c r="F255"/>
       <c r="G255"/>
       <c r="H255" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="I255"/>
       <c r="J255"/>
@@ -6319,7 +6145,7 @@
       <c r="F256"/>
       <c r="G256"/>
       <c r="H256" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="I256"/>
       <c r="J256"/>
@@ -6330,7 +6156,7 @@
         <v>45046</v>
       </c>
       <c r="B257" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C257"/>
       <c r="D257"/>
@@ -6338,7 +6164,7 @@
       <c r="F257"/>
       <c r="G257"/>
       <c r="H257" t="s">
-        <v>244</v>
+        <v>51</v>
       </c>
       <c r="I257"/>
       <c r="J257"/>
@@ -6357,7 +6183,7 @@
       <c r="F258"/>
       <c r="G258"/>
       <c r="H258" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="I258"/>
       <c r="J258"/>
@@ -6376,7 +6202,7 @@
       <c r="F259"/>
       <c r="G259"/>
       <c r="H259" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="I259"/>
       <c r="J259"/>
@@ -6395,7 +6221,7 @@
       <c r="F260"/>
       <c r="G260"/>
       <c r="H260" t="s">
-        <v>33</v>
+        <v>214</v>
       </c>
       <c r="I260"/>
       <c r="J260"/>
@@ -6414,7 +6240,7 @@
       <c r="F261"/>
       <c r="G261"/>
       <c r="H261" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="I261"/>
       <c r="J261"/>
@@ -6425,7 +6251,7 @@
         <v>45107</v>
       </c>
       <c r="B262" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C262"/>
       <c r="D262"/>
@@ -6433,7 +6259,7 @@
       <c r="F262"/>
       <c r="G262"/>
       <c r="H262" t="s">
-        <v>48</v>
+        <v>228</v>
       </c>
       <c r="I262"/>
       <c r="J262"/>
@@ -6444,7 +6270,7 @@
         <v>45107</v>
       </c>
       <c r="B263" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C263"/>
       <c r="D263"/>
@@ -6452,7 +6278,7 @@
       <c r="F263"/>
       <c r="G263"/>
       <c r="H263" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="I263"/>
       <c r="J263"/>
@@ -6463,7 +6289,7 @@
         <v>45107</v>
       </c>
       <c r="B264" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C264"/>
       <c r="D264"/>
@@ -6471,7 +6297,7 @@
       <c r="F264"/>
       <c r="G264"/>
       <c r="H264" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="I264"/>
       <c r="J264"/>
@@ -6482,7 +6308,7 @@
         <v>45107</v>
       </c>
       <c r="B265" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C265"/>
       <c r="D265"/>
@@ -6490,7 +6316,7 @@
       <c r="F265"/>
       <c r="G265"/>
       <c r="H265" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="I265"/>
       <c r="J265"/>
@@ -6501,7 +6327,7 @@
         <v>45138</v>
       </c>
       <c r="B266" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C266"/>
       <c r="D266"/>
@@ -6509,7 +6335,7 @@
       <c r="F266"/>
       <c r="G266"/>
       <c r="H266" t="s">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="I266"/>
       <c r="J266"/>
@@ -6520,7 +6346,7 @@
         <v>45138</v>
       </c>
       <c r="B267" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C267"/>
       <c r="D267"/>
@@ -6528,7 +6354,7 @@
       <c r="F267"/>
       <c r="G267"/>
       <c r="H267" t="s">
-        <v>120</v>
+        <v>209</v>
       </c>
       <c r="I267"/>
       <c r="J267"/>
@@ -6539,7 +6365,7 @@
         <v>45138</v>
       </c>
       <c r="B268" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C268"/>
       <c r="D268"/>
@@ -6547,7 +6373,7 @@
       <c r="F268"/>
       <c r="G268"/>
       <c r="H268" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="I268"/>
       <c r="J268"/>
@@ -6558,7 +6384,7 @@
         <v>45138</v>
       </c>
       <c r="B269" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C269"/>
       <c r="D269"/>
@@ -6566,7 +6392,7 @@
       <c r="F269"/>
       <c r="G269"/>
       <c r="H269" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="I269"/>
       <c r="J269"/>
@@ -6585,7 +6411,7 @@
       <c r="F270"/>
       <c r="G270"/>
       <c r="H270" t="s">
-        <v>44</v>
+        <v>233</v>
       </c>
       <c r="I270"/>
       <c r="J270"/>
@@ -6604,7 +6430,7 @@
       <c r="F271"/>
       <c r="G271"/>
       <c r="H271" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="I271"/>
       <c r="J271"/>
@@ -6615,7 +6441,7 @@
         <v>45169</v>
       </c>
       <c r="B272" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C272"/>
       <c r="D272"/>
@@ -6623,7 +6449,7 @@
       <c r="F272"/>
       <c r="G272"/>
       <c r="H272" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="I272"/>
       <c r="J272"/>
@@ -6634,7 +6460,7 @@
         <v>45169</v>
       </c>
       <c r="B273" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C273"/>
       <c r="D273"/>
@@ -6642,7 +6468,7 @@
       <c r="F273"/>
       <c r="G273"/>
       <c r="H273" t="s">
-        <v>254</v>
+        <v>175</v>
       </c>
       <c r="I273"/>
       <c r="J273"/>
@@ -6653,7 +6479,7 @@
         <v>45199</v>
       </c>
       <c r="B274" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C274"/>
       <c r="D274"/>
@@ -6661,7 +6487,7 @@
       <c r="F274"/>
       <c r="G274"/>
       <c r="H274" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="I274"/>
       <c r="J274"/>
@@ -6680,7 +6506,7 @@
       <c r="F275"/>
       <c r="G275"/>
       <c r="H275" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="I275"/>
       <c r="J275"/>
@@ -6699,7 +6525,7 @@
       <c r="F276"/>
       <c r="G276"/>
       <c r="H276" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="I276"/>
       <c r="J276"/>
@@ -6710,7 +6536,7 @@
         <v>45199</v>
       </c>
       <c r="B277" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C277"/>
       <c r="D277"/>
@@ -6718,7 +6544,7 @@
       <c r="F277"/>
       <c r="G277"/>
       <c r="H277" t="s">
-        <v>257</v>
+        <v>35</v>
       </c>
       <c r="I277"/>
       <c r="J277"/>
@@ -6729,7 +6555,7 @@
         <v>45230</v>
       </c>
       <c r="B278" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C278"/>
       <c r="D278"/>
@@ -6737,7 +6563,7 @@
       <c r="F278"/>
       <c r="G278"/>
       <c r="H278" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="I278"/>
       <c r="J278"/>
@@ -6748,7 +6574,7 @@
         <v>45230</v>
       </c>
       <c r="B279" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C279"/>
       <c r="D279"/>
@@ -6756,7 +6582,7 @@
       <c r="F279"/>
       <c r="G279"/>
       <c r="H279" t="s">
-        <v>259</v>
+        <v>52</v>
       </c>
       <c r="I279"/>
       <c r="J279"/>
@@ -6767,7 +6593,7 @@
         <v>45230</v>
       </c>
       <c r="B280" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C280"/>
       <c r="D280"/>
@@ -6775,7 +6601,7 @@
       <c r="F280"/>
       <c r="G280"/>
       <c r="H280" t="s">
-        <v>260</v>
+        <v>114</v>
       </c>
       <c r="I280"/>
       <c r="J280"/>
@@ -6786,7 +6612,7 @@
         <v>45230</v>
       </c>
       <c r="B281" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C281"/>
       <c r="D281"/>
@@ -6794,7 +6620,7 @@
       <c r="F281"/>
       <c r="G281"/>
       <c r="H281" t="s">
-        <v>261</v>
+        <v>35</v>
       </c>
       <c r="I281"/>
       <c r="J281"/>
@@ -6805,7 +6631,7 @@
         <v>45260</v>
       </c>
       <c r="B282" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C282"/>
       <c r="D282"/>
@@ -6813,7 +6639,7 @@
       <c r="F282"/>
       <c r="G282"/>
       <c r="H282" t="s">
-        <v>262</v>
+        <v>188</v>
       </c>
       <c r="I282"/>
       <c r="J282"/>
@@ -6824,7 +6650,7 @@
         <v>45260</v>
       </c>
       <c r="B283" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C283"/>
       <c r="D283"/>
@@ -6832,7 +6658,7 @@
       <c r="F283"/>
       <c r="G283"/>
       <c r="H283" t="s">
-        <v>96</v>
+        <v>239</v>
       </c>
       <c r="I283"/>
       <c r="J283"/>
@@ -6843,7 +6669,7 @@
         <v>45260</v>
       </c>
       <c r="B284" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C284"/>
       <c r="D284"/>
@@ -6851,7 +6677,7 @@
       <c r="F284"/>
       <c r="G284"/>
       <c r="H284" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="I284"/>
       <c r="J284"/>
@@ -6862,7 +6688,7 @@
         <v>45260</v>
       </c>
       <c r="B285" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C285"/>
       <c r="D285"/>
@@ -6870,7 +6696,7 @@
       <c r="F285"/>
       <c r="G285"/>
       <c r="H285" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="I285"/>
       <c r="J285"/>
@@ -6881,7 +6707,7 @@
         <v>45291</v>
       </c>
       <c r="B286" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C286"/>
       <c r="D286"/>
@@ -6889,7 +6715,7 @@
       <c r="F286"/>
       <c r="G286"/>
       <c r="H286" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="I286"/>
       <c r="J286"/>
@@ -6908,7 +6734,7 @@
       <c r="F287"/>
       <c r="G287"/>
       <c r="H287" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="I287"/>
       <c r="J287"/>
@@ -6919,7 +6745,7 @@
         <v>45291</v>
       </c>
       <c r="B288" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C288"/>
       <c r="D288"/>
@@ -6927,7 +6753,7 @@
       <c r="F288"/>
       <c r="G288"/>
       <c r="H288" t="s">
-        <v>266</v>
+        <v>57</v>
       </c>
       <c r="I288"/>
       <c r="J288"/>
@@ -6946,7 +6772,7 @@
       <c r="F289"/>
       <c r="G289"/>
       <c r="H289" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="I289"/>
       <c r="J289"/>
@@ -6957,7 +6783,7 @@
         <v>45322</v>
       </c>
       <c r="B290" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C290"/>
       <c r="D290"/>
@@ -6965,7 +6791,7 @@
       <c r="F290"/>
       <c r="G290"/>
       <c r="H290" t="s">
-        <v>268</v>
+        <v>52</v>
       </c>
       <c r="I290"/>
       <c r="J290"/>
@@ -6976,7 +6802,7 @@
         <v>45322</v>
       </c>
       <c r="B291" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C291"/>
       <c r="D291"/>
@@ -6984,7 +6810,7 @@
       <c r="F291"/>
       <c r="G291"/>
       <c r="H291" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="I291"/>
       <c r="J291"/>
@@ -6995,7 +6821,7 @@
         <v>45322</v>
       </c>
       <c r="B292" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C292"/>
       <c r="D292"/>
@@ -7003,7 +6829,7 @@
       <c r="F292"/>
       <c r="G292"/>
       <c r="H292" t="s">
-        <v>86</v>
+        <v>244</v>
       </c>
       <c r="I292"/>
       <c r="J292"/>
@@ -7014,7 +6840,7 @@
         <v>45322</v>
       </c>
       <c r="B293" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C293"/>
       <c r="D293"/>
@@ -7022,7 +6848,7 @@
       <c r="F293"/>
       <c r="G293"/>
       <c r="H293" t="s">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="I293"/>
       <c r="J293"/>
@@ -7033,7 +6859,7 @@
         <v>45351</v>
       </c>
       <c r="B294" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C294"/>
       <c r="D294"/>
@@ -7041,7 +6867,7 @@
       <c r="F294"/>
       <c r="G294"/>
       <c r="H294" t="s">
-        <v>270</v>
+        <v>98</v>
       </c>
       <c r="I294"/>
       <c r="J294"/>
@@ -7052,7 +6878,7 @@
         <v>45351</v>
       </c>
       <c r="B295" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C295"/>
       <c r="D295"/>
@@ -7060,7 +6886,7 @@
       <c r="F295"/>
       <c r="G295"/>
       <c r="H295" t="s">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="I295"/>
       <c r="J295"/>
@@ -7079,7 +6905,7 @@
       <c r="F296"/>
       <c r="G296"/>
       <c r="H296" t="s">
-        <v>271</v>
+        <v>246</v>
       </c>
       <c r="I296"/>
       <c r="J296"/>
@@ -7090,7 +6916,7 @@
         <v>45351</v>
       </c>
       <c r="B297" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C297"/>
       <c r="D297"/>
@@ -7098,7 +6924,7 @@
       <c r="F297"/>
       <c r="G297"/>
       <c r="H297" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="I297"/>
       <c r="J297"/>
@@ -7109,7 +6935,7 @@
         <v>45382</v>
       </c>
       <c r="B298" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C298"/>
       <c r="D298"/>
@@ -7117,7 +6943,7 @@
       <c r="F298"/>
       <c r="G298"/>
       <c r="H298" t="s">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="I298"/>
       <c r="J298"/>
@@ -7128,7 +6954,7 @@
         <v>45382</v>
       </c>
       <c r="B299" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C299"/>
       <c r="D299"/>
@@ -7136,7 +6962,7 @@
       <c r="F299"/>
       <c r="G299"/>
       <c r="H299" t="s">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="I299"/>
       <c r="J299"/>
@@ -7147,7 +6973,7 @@
         <v>45382</v>
       </c>
       <c r="B300" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C300"/>
       <c r="D300"/>
@@ -7155,7 +6981,7 @@
       <c r="F300"/>
       <c r="G300"/>
       <c r="H300" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="I300"/>
       <c r="J300"/>
@@ -7166,7 +6992,7 @@
         <v>45382</v>
       </c>
       <c r="B301" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C301"/>
       <c r="D301"/>
@@ -7174,7 +7000,7 @@
       <c r="F301"/>
       <c r="G301"/>
       <c r="H301" t="s">
-        <v>276</v>
+        <v>31</v>
       </c>
       <c r="I301"/>
       <c r="J301"/>
@@ -7185,7 +7011,7 @@
         <v>45412</v>
       </c>
       <c r="B302" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C302"/>
       <c r="D302"/>
@@ -7193,7 +7019,7 @@
       <c r="F302"/>
       <c r="G302"/>
       <c r="H302" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="I302"/>
       <c r="J302"/>
@@ -7212,7 +7038,7 @@
       <c r="F303"/>
       <c r="G303"/>
       <c r="H303" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="I303"/>
       <c r="J303"/>
@@ -7223,7 +7049,7 @@
         <v>45412</v>
       </c>
       <c r="B304" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C304"/>
       <c r="D304"/>
@@ -7231,7 +7057,7 @@
       <c r="F304"/>
       <c r="G304"/>
       <c r="H304" t="s">
-        <v>279</v>
+        <v>39</v>
       </c>
       <c r="I304"/>
       <c r="J304"/>
@@ -7242,7 +7068,7 @@
         <v>45412</v>
       </c>
       <c r="B305" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C305"/>
       <c r="D305"/>
@@ -7250,7 +7076,7 @@
       <c r="F305"/>
       <c r="G305"/>
       <c r="H305" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="I305"/>
       <c r="J305"/>
@@ -7261,7 +7087,7 @@
         <v>45443</v>
       </c>
       <c r="B306" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C306"/>
       <c r="D306"/>
@@ -7269,7 +7095,7 @@
       <c r="F306"/>
       <c r="G306"/>
       <c r="H306" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="I306"/>
       <c r="J306"/>
@@ -7288,7 +7114,7 @@
       <c r="F307"/>
       <c r="G307"/>
       <c r="H307" t="s">
-        <v>278</v>
+        <v>61</v>
       </c>
       <c r="I307"/>
       <c r="J307"/>
@@ -7307,7 +7133,7 @@
       <c r="F308"/>
       <c r="G308"/>
       <c r="H308" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="I308"/>
       <c r="J308"/>
@@ -7318,7 +7144,7 @@
         <v>45443</v>
       </c>
       <c r="B309" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C309"/>
       <c r="D309"/>
@@ -7326,7 +7152,7 @@
       <c r="F309"/>
       <c r="G309"/>
       <c r="H309" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="I309"/>
       <c r="J309"/>
@@ -7337,7 +7163,7 @@
         <v>45473</v>
       </c>
       <c r="B310" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C310"/>
       <c r="D310"/>
@@ -7345,7 +7171,7 @@
       <c r="F310"/>
       <c r="G310"/>
       <c r="H310" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="I310"/>
       <c r="J310"/>
@@ -7356,7 +7182,7 @@
         <v>45473</v>
       </c>
       <c r="B311" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C311"/>
       <c r="D311"/>
@@ -7364,7 +7190,7 @@
       <c r="F311"/>
       <c r="G311"/>
       <c r="H311" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="I311"/>
       <c r="J311"/>
@@ -7375,7 +7201,7 @@
         <v>45473</v>
       </c>
       <c r="B312" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C312"/>
       <c r="D312"/>
@@ -7383,7 +7209,7 @@
       <c r="F312"/>
       <c r="G312"/>
       <c r="H312" t="s">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="I312"/>
       <c r="J312"/>
@@ -7394,7 +7220,7 @@
         <v>45473</v>
       </c>
       <c r="B313" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C313"/>
       <c r="D313"/>
@@ -7402,7 +7228,7 @@
       <c r="F313"/>
       <c r="G313"/>
       <c r="H313" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="I313"/>
       <c r="J313"/>
@@ -7413,7 +7239,7 @@
         <v>45504</v>
       </c>
       <c r="B314" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C314"/>
       <c r="D314"/>
@@ -7421,7 +7247,7 @@
       <c r="F314"/>
       <c r="G314"/>
       <c r="H314" t="s">
-        <v>29</v>
+        <v>260</v>
       </c>
       <c r="I314"/>
       <c r="J314"/>
@@ -7432,7 +7258,7 @@
         <v>45504</v>
       </c>
       <c r="B315" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C315"/>
       <c r="D315"/>
@@ -7440,7 +7266,7 @@
       <c r="F315"/>
       <c r="G315"/>
       <c r="H315" t="s">
-        <v>287</v>
+        <v>186</v>
       </c>
       <c r="I315"/>
       <c r="J315"/>
@@ -7451,7 +7277,7 @@
         <v>45504</v>
       </c>
       <c r="B316" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C316"/>
       <c r="D316"/>
@@ -7459,7 +7285,7 @@
       <c r="F316"/>
       <c r="G316"/>
       <c r="H316" t="s">
-        <v>288</v>
+        <v>88</v>
       </c>
       <c r="I316"/>
       <c r="J316"/>
@@ -7470,7 +7296,7 @@
         <v>45504</v>
       </c>
       <c r="B317" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C317"/>
       <c r="D317"/>
@@ -7478,7 +7304,7 @@
       <c r="F317"/>
       <c r="G317"/>
       <c r="H317" t="s">
-        <v>289</v>
+        <v>92</v>
       </c>
       <c r="I317"/>
       <c r="J317"/>
@@ -7489,7 +7315,7 @@
         <v>45535</v>
       </c>
       <c r="B318" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C318"/>
       <c r="D318"/>
@@ -7497,7 +7323,7 @@
       <c r="F318"/>
       <c r="G318"/>
       <c r="H318" t="s">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="I318"/>
       <c r="J318"/>
@@ -7508,7 +7334,7 @@
         <v>45535</v>
       </c>
       <c r="B319" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C319"/>
       <c r="D319"/>
@@ -7516,7 +7342,7 @@
       <c r="F319"/>
       <c r="G319"/>
       <c r="H319" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="I319"/>
       <c r="J319"/>
@@ -7527,7 +7353,7 @@
         <v>45535</v>
       </c>
       <c r="B320" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C320"/>
       <c r="D320"/>
@@ -7535,7 +7361,7 @@
       <c r="F320"/>
       <c r="G320"/>
       <c r="H320" t="s">
-        <v>291</v>
+        <v>189</v>
       </c>
       <c r="I320"/>
       <c r="J320"/>
@@ -7546,7 +7372,7 @@
         <v>45535</v>
       </c>
       <c r="B321" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C321"/>
       <c r="D321"/>
@@ -7554,7 +7380,7 @@
       <c r="F321"/>
       <c r="G321"/>
       <c r="H321" t="s">
-        <v>292</v>
+        <v>40</v>
       </c>
       <c r="I321"/>
       <c r="J321"/>
@@ -7573,7 +7399,7 @@
       <c r="F322"/>
       <c r="G322"/>
       <c r="H322" t="s">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="I322"/>
       <c r="J322"/>
@@ -7592,7 +7418,7 @@
       <c r="F323"/>
       <c r="G323"/>
       <c r="H323" t="s">
-        <v>96</v>
+        <v>256</v>
       </c>
       <c r="I323"/>
       <c r="J323"/>
@@ -7603,7 +7429,7 @@
         <v>45565</v>
       </c>
       <c r="B324" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C324"/>
       <c r="D324"/>
@@ -7611,7 +7437,7 @@
       <c r="F324"/>
       <c r="G324"/>
       <c r="H324" t="s">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="I324"/>
       <c r="J324"/>
@@ -7622,7 +7448,7 @@
         <v>45565</v>
       </c>
       <c r="B325" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C325"/>
       <c r="D325"/>
@@ -7630,7 +7456,7 @@
       <c r="F325"/>
       <c r="G325"/>
       <c r="H325" t="s">
-        <v>295</v>
+        <v>175</v>
       </c>
       <c r="I325"/>
       <c r="J325"/>
@@ -7641,7 +7467,7 @@
         <v>45596</v>
       </c>
       <c r="B326" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C326"/>
       <c r="D326"/>
@@ -7649,7 +7475,7 @@
       <c r="F326"/>
       <c r="G326"/>
       <c r="H326" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="I326"/>
       <c r="J326"/>
@@ -7660,7 +7486,7 @@
         <v>45596</v>
       </c>
       <c r="B327" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C327"/>
       <c r="D327"/>
@@ -7668,7 +7494,7 @@
       <c r="F327"/>
       <c r="G327"/>
       <c r="H327" t="s">
-        <v>258</v>
+        <v>86</v>
       </c>
       <c r="I327"/>
       <c r="J327"/>
@@ -7679,7 +7505,7 @@
         <v>45596</v>
       </c>
       <c r="B328" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C328"/>
       <c r="D328"/>
@@ -7687,7 +7513,7 @@
       <c r="F328"/>
       <c r="G328"/>
       <c r="H328" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="I328"/>
       <c r="J328"/>
@@ -7698,7 +7524,7 @@
         <v>45596</v>
       </c>
       <c r="B329" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C329"/>
       <c r="D329"/>
@@ -7706,7 +7532,7 @@
       <c r="F329"/>
       <c r="G329"/>
       <c r="H329" t="s">
-        <v>298</v>
+        <v>25</v>
       </c>
       <c r="I329"/>
       <c r="J329"/>
@@ -7717,7 +7543,7 @@
         <v>45626</v>
       </c>
       <c r="B330" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C330"/>
       <c r="D330"/>
@@ -7725,7 +7551,7 @@
       <c r="F330"/>
       <c r="G330"/>
       <c r="H330" t="s">
-        <v>299</v>
+        <v>90</v>
       </c>
       <c r="I330"/>
       <c r="J330"/>
@@ -7736,7 +7562,7 @@
         <v>45626</v>
       </c>
       <c r="B331" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C331"/>
       <c r="D331"/>
@@ -7744,7 +7570,7 @@
       <c r="F331"/>
       <c r="G331"/>
       <c r="H331" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="I331"/>
       <c r="J331"/>
@@ -7755,7 +7581,7 @@
         <v>45626</v>
       </c>
       <c r="B332" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C332"/>
       <c r="D332"/>
@@ -7763,7 +7589,7 @@
       <c r="F332"/>
       <c r="G332"/>
       <c r="H332" t="s">
-        <v>301</v>
+        <v>219</v>
       </c>
       <c r="I332"/>
       <c r="J332"/>
@@ -7774,7 +7600,7 @@
         <v>45626</v>
       </c>
       <c r="B333" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C333"/>
       <c r="D333"/>
@@ -7782,7 +7608,7 @@
       <c r="F333"/>
       <c r="G333"/>
       <c r="H333" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="I333"/>
       <c r="J333"/>
@@ -7801,7 +7627,7 @@
       <c r="F334"/>
       <c r="G334"/>
       <c r="H334" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="I334"/>
       <c r="J334"/>
@@ -7812,7 +7638,7 @@
         <v>45657</v>
       </c>
       <c r="B335" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C335"/>
       <c r="D335"/>
@@ -7820,7 +7646,7 @@
       <c r="F335"/>
       <c r="G335"/>
       <c r="H335" t="s">
-        <v>304</v>
+        <v>222</v>
       </c>
       <c r="I335"/>
       <c r="J335"/>
@@ -7831,7 +7657,7 @@
         <v>45657</v>
       </c>
       <c r="B336" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C336"/>
       <c r="D336"/>
@@ -7839,7 +7665,7 @@
       <c r="F336"/>
       <c r="G336"/>
       <c r="H336" t="s">
-        <v>305</v>
+        <v>264</v>
       </c>
       <c r="I336"/>
       <c r="J336"/>
@@ -7850,7 +7676,7 @@
         <v>45657</v>
       </c>
       <c r="B337" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C337"/>
       <c r="D337"/>
@@ -7858,7 +7684,7 @@
       <c r="F337"/>
       <c r="G337"/>
       <c r="H337" t="s">
-        <v>306</v>
+        <v>217</v>
       </c>
       <c r="I337"/>
       <c r="J337"/>
@@ -7869,7 +7695,7 @@
         <v>45688</v>
       </c>
       <c r="B338" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C338"/>
       <c r="D338"/>
@@ -7877,7 +7703,7 @@
       <c r="F338"/>
       <c r="G338"/>
       <c r="H338" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="I338"/>
       <c r="J338"/>
@@ -7896,7 +7722,7 @@
       <c r="F339"/>
       <c r="G339"/>
       <c r="H339" t="s">
-        <v>307</v>
+        <v>144</v>
       </c>
       <c r="I339"/>
       <c r="J339"/>
@@ -7907,7 +7733,7 @@
         <v>45688</v>
       </c>
       <c r="B340" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C340"/>
       <c r="D340"/>
@@ -7915,7 +7741,7 @@
       <c r="F340"/>
       <c r="G340"/>
       <c r="H340" t="s">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="I340"/>
       <c r="J340"/>
@@ -7926,7 +7752,7 @@
         <v>45688</v>
       </c>
       <c r="B341" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C341"/>
       <c r="D341"/>
@@ -7934,7 +7760,7 @@
       <c r="F341"/>
       <c r="G341"/>
       <c r="H341" t="s">
-        <v>308</v>
+        <v>241</v>
       </c>
       <c r="I341"/>
       <c r="J341"/>
@@ -7945,7 +7771,7 @@
         <v>45716</v>
       </c>
       <c r="B342" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C342"/>
       <c r="D342"/>
@@ -7953,7 +7779,7 @@
       <c r="F342"/>
       <c r="G342"/>
       <c r="H342" t="s">
-        <v>309</v>
+        <v>116</v>
       </c>
       <c r="I342"/>
       <c r="J342"/>
@@ -7972,7 +7798,7 @@
       <c r="F343"/>
       <c r="G343"/>
       <c r="H343" t="s">
-        <v>310</v>
+        <v>271</v>
       </c>
       <c r="I343"/>
       <c r="J343"/>
@@ -7983,7 +7809,7 @@
         <v>45716</v>
       </c>
       <c r="B344" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C344"/>
       <c r="D344"/>
@@ -7991,7 +7817,7 @@
       <c r="F344"/>
       <c r="G344"/>
       <c r="H344" t="s">
-        <v>311</v>
+        <v>272</v>
       </c>
       <c r="I344"/>
       <c r="J344"/>
@@ -8002,7 +7828,7 @@
         <v>45716</v>
       </c>
       <c r="B345" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C345"/>
       <c r="D345"/>
@@ -8010,7 +7836,7 @@
       <c r="F345"/>
       <c r="G345"/>
       <c r="H345" t="s">
-        <v>312</v>
+        <v>273</v>
       </c>
       <c r="I345"/>
       <c r="J345"/>
@@ -8029,7 +7855,7 @@
       <c r="F346"/>
       <c r="G346"/>
       <c r="H346" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="I346"/>
       <c r="J346"/>
@@ -8040,7 +7866,7 @@
         <v>45747</v>
       </c>
       <c r="B347" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C347"/>
       <c r="D347"/>
@@ -8048,7 +7874,7 @@
       <c r="F347"/>
       <c r="G347"/>
       <c r="H347" t="s">
-        <v>313</v>
+        <v>87</v>
       </c>
       <c r="I347"/>
       <c r="J347"/>
@@ -8059,7 +7885,7 @@
         <v>45747</v>
       </c>
       <c r="B348" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C348"/>
       <c r="D348"/>
@@ -8067,7 +7893,7 @@
       <c r="F348"/>
       <c r="G348"/>
       <c r="H348" t="s">
-        <v>314</v>
+        <v>274</v>
       </c>
       <c r="I348"/>
       <c r="J348"/>
@@ -8078,7 +7904,7 @@
         <v>45747</v>
       </c>
       <c r="B349" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C349"/>
       <c r="D349"/>
@@ -8086,7 +7912,7 @@
       <c r="F349"/>
       <c r="G349"/>
       <c r="H349" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="I349"/>
       <c r="J349"/>
@@ -8105,7 +7931,7 @@
       <c r="F350"/>
       <c r="G350"/>
       <c r="H350" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="I350"/>
       <c r="J350"/>
@@ -8116,7 +7942,7 @@
         <v>45777</v>
       </c>
       <c r="B351" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C351"/>
       <c r="D351"/>
@@ -8124,7 +7950,7 @@
       <c r="F351"/>
       <c r="G351"/>
       <c r="H351" t="s">
-        <v>316</v>
+        <v>61</v>
       </c>
       <c r="I351"/>
       <c r="J351"/>
@@ -8135,7 +7961,7 @@
         <v>45777</v>
       </c>
       <c r="B352" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C352"/>
       <c r="D352"/>
@@ -8143,7 +7969,7 @@
       <c r="F352"/>
       <c r="G352"/>
       <c r="H352" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="I352"/>
       <c r="J352"/>
@@ -8162,7 +7988,7 @@
       <c r="F353"/>
       <c r="G353"/>
       <c r="H353" t="s">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="I353"/>
       <c r="J353"/>
@@ -8173,7 +7999,7 @@
         <v>45808</v>
       </c>
       <c r="B354" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C354"/>
       <c r="D354"/>
@@ -8181,7 +8007,7 @@
       <c r="F354"/>
       <c r="G354"/>
       <c r="H354" t="s">
-        <v>318</v>
+        <v>277</v>
       </c>
       <c r="I354"/>
       <c r="J354"/>
@@ -8200,7 +8026,7 @@
       <c r="F355"/>
       <c r="G355"/>
       <c r="H355" t="s">
-        <v>319</v>
+        <v>48</v>
       </c>
       <c r="I355"/>
       <c r="J355"/>
@@ -8219,7 +8045,7 @@
       <c r="F356"/>
       <c r="G356"/>
       <c r="H356" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="I356"/>
       <c r="J356"/>
@@ -8230,7 +8056,7 @@
         <v>45808</v>
       </c>
       <c r="B357" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C357"/>
       <c r="D357"/>
@@ -8238,7 +8064,7 @@
       <c r="F357"/>
       <c r="G357"/>
       <c r="H357" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="I357"/>
       <c r="J357"/>
@@ -8249,7 +8075,7 @@
         <v>45838</v>
       </c>
       <c r="B358" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C358"/>
       <c r="D358"/>
@@ -8257,7 +8083,7 @@
       <c r="F358"/>
       <c r="G358"/>
       <c r="H358" t="s">
-        <v>321</v>
+        <v>279</v>
       </c>
       <c r="I358"/>
       <c r="J358"/>
@@ -8268,7 +8094,7 @@
         <v>45838</v>
       </c>
       <c r="B359" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C359"/>
       <c r="D359"/>
@@ -8276,7 +8102,7 @@
       <c r="F359"/>
       <c r="G359"/>
       <c r="H359" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="I359"/>
       <c r="J359"/>
@@ -8287,7 +8113,7 @@
         <v>45838</v>
       </c>
       <c r="B360" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C360"/>
       <c r="D360"/>
@@ -8295,7 +8121,7 @@
       <c r="F360"/>
       <c r="G360"/>
       <c r="H360" t="s">
-        <v>322</v>
+        <v>42</v>
       </c>
       <c r="I360"/>
       <c r="J360"/>
@@ -8306,7 +8132,7 @@
         <v>45838</v>
       </c>
       <c r="B361" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C361"/>
       <c r="D361"/>
@@ -8314,7 +8140,7 @@
       <c r="F361"/>
       <c r="G361"/>
       <c r="H361" t="s">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="I361"/>
       <c r="J361"/>
@@ -8333,7 +8159,7 @@
       <c r="F362"/>
       <c r="G362"/>
       <c r="H362" t="s">
-        <v>324</v>
+        <v>104</v>
       </c>
       <c r="I362"/>
       <c r="J362"/>
@@ -8344,7 +8170,7 @@
         <v>45869</v>
       </c>
       <c r="B363" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C363"/>
       <c r="D363"/>
@@ -8352,7 +8178,7 @@
       <c r="F363"/>
       <c r="G363"/>
       <c r="H363" t="s">
-        <v>303</v>
+        <v>240</v>
       </c>
       <c r="I363"/>
       <c r="J363"/>
@@ -8363,7 +8189,7 @@
         <v>45869</v>
       </c>
       <c r="B364" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C364"/>
       <c r="D364"/>
@@ -8371,7 +8197,7 @@
       <c r="F364"/>
       <c r="G364"/>
       <c r="H364" t="s">
-        <v>325</v>
+        <v>46</v>
       </c>
       <c r="I364"/>
       <c r="J364"/>
@@ -8390,7 +8216,7 @@
       <c r="F365"/>
       <c r="G365"/>
       <c r="H365" t="s">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="I365"/>
       <c r="J365"/>
@@ -8401,7 +8227,7 @@
         <v>45900</v>
       </c>
       <c r="B366" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C366"/>
       <c r="D366"/>
@@ -8409,7 +8235,7 @@
       <c r="F366"/>
       <c r="G366"/>
       <c r="H366" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="I366"/>
       <c r="J366"/>
@@ -8420,7 +8246,7 @@
         <v>45900</v>
       </c>
       <c r="B367" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C367"/>
       <c r="D367"/>
@@ -8428,7 +8254,7 @@
       <c r="F367"/>
       <c r="G367"/>
       <c r="H367" t="s">
-        <v>327</v>
+        <v>92</v>
       </c>
       <c r="I367"/>
       <c r="J367"/>
@@ -8447,7 +8273,7 @@
       <c r="F368"/>
       <c r="G368"/>
       <c r="H368" t="s">
-        <v>328</v>
+        <v>283</v>
       </c>
       <c r="I368"/>
       <c r="J368"/>
@@ -8458,7 +8284,7 @@
         <v>45900</v>
       </c>
       <c r="B369" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C369"/>
       <c r="D369"/>
@@ -8466,7 +8292,7 @@
       <c r="F369"/>
       <c r="G369"/>
       <c r="H369" t="s">
-        <v>329</v>
+        <v>85</v>
       </c>
       <c r="I369"/>
       <c r="J369"/>
@@ -8485,7 +8311,7 @@
       <c r="F370"/>
       <c r="G370"/>
       <c r="H370" t="s">
-        <v>330</v>
+        <v>273</v>
       </c>
       <c r="I370"/>
       <c r="J370"/>
@@ -8504,7 +8330,7 @@
       <c r="F371"/>
       <c r="G371"/>
       <c r="H371" t="s">
-        <v>51</v>
+        <v>284</v>
       </c>
       <c r="I371"/>
       <c r="J371"/>
@@ -8523,7 +8349,7 @@
       <c r="F372"/>
       <c r="G372"/>
       <c r="H372" t="s">
-        <v>331</v>
+        <v>285</v>
       </c>
       <c r="I372"/>
       <c r="J372"/>
@@ -8542,7 +8368,7 @@
       <c r="F373"/>
       <c r="G373"/>
       <c r="H373" t="s">
-        <v>332</v>
+        <v>286</v>
       </c>
       <c r="I373"/>
       <c r="J373"/>
@@ -8553,7 +8379,7 @@
         <v>45961</v>
       </c>
       <c r="B374" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C374"/>
       <c r="D374"/>
@@ -8561,7 +8387,7 @@
       <c r="F374"/>
       <c r="G374"/>
       <c r="H374" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="I374"/>
       <c r="J374"/>
@@ -8572,7 +8398,7 @@
         <v>45961</v>
       </c>
       <c r="B375" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C375"/>
       <c r="D375"/>
@@ -8580,7 +8406,7 @@
       <c r="F375"/>
       <c r="G375"/>
       <c r="H375" t="s">
-        <v>289</v>
+        <v>46</v>
       </c>
       <c r="I375"/>
       <c r="J375"/>
@@ -8591,7 +8417,7 @@
         <v>45961</v>
       </c>
       <c r="B376" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C376"/>
       <c r="D376"/>
@@ -8599,7 +8425,7 @@
       <c r="F376"/>
       <c r="G376"/>
       <c r="H376" t="s">
-        <v>333</v>
+        <v>198</v>
       </c>
       <c r="I376"/>
       <c r="J376"/>
@@ -8610,7 +8436,7 @@
         <v>45961</v>
       </c>
       <c r="B377" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C377"/>
       <c r="D377"/>
@@ -8618,7 +8444,7 @@
       <c r="F377"/>
       <c r="G377"/>
       <c r="H377" t="s">
-        <v>334</v>
+        <v>172</v>
       </c>
       <c r="I377"/>
       <c r="J377"/>
@@ -8629,7 +8455,7 @@
         <v>45991</v>
       </c>
       <c r="B378" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C378"/>
       <c r="D378"/>
@@ -8637,7 +8463,7 @@
       <c r="F378"/>
       <c r="G378"/>
       <c r="H378" t="s">
-        <v>335</v>
+        <v>257</v>
       </c>
       <c r="I378"/>
       <c r="J378"/>
@@ -8648,7 +8474,7 @@
         <v>45991</v>
       </c>
       <c r="B379" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C379"/>
       <c r="D379"/>
@@ -8656,7 +8482,7 @@
       <c r="F379"/>
       <c r="G379"/>
       <c r="H379" t="s">
-        <v>336</v>
+        <v>264</v>
       </c>
       <c r="I379"/>
       <c r="J379"/>
@@ -8667,7 +8493,7 @@
         <v>45991</v>
       </c>
       <c r="B380" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C380"/>
       <c r="D380"/>
@@ -8675,7 +8501,7 @@
       <c r="F380"/>
       <c r="G380"/>
       <c r="H380" t="s">
-        <v>337</v>
+        <v>115</v>
       </c>
       <c r="I380"/>
       <c r="J380"/>
@@ -8686,7 +8512,7 @@
         <v>45991</v>
       </c>
       <c r="B381" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C381"/>
       <c r="D381"/>
@@ -8694,7 +8520,7 @@
       <c r="F381"/>
       <c r="G381"/>
       <c r="H381" t="s">
-        <v>338</v>
+        <v>277</v>
       </c>
       <c r="I381"/>
       <c r="J381"/>
@@ -8705,7 +8531,7 @@
         <v>46022</v>
       </c>
       <c r="B382" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C382"/>
       <c r="D382"/>
@@ -8713,7 +8539,7 @@
       <c r="F382"/>
       <c r="G382"/>
       <c r="H382" t="s">
-        <v>339</v>
+        <v>281</v>
       </c>
       <c r="I382"/>
       <c r="J382"/>
@@ -8724,7 +8550,7 @@
         <v>46022</v>
       </c>
       <c r="B383" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C383"/>
       <c r="D383"/>
@@ -8732,7 +8558,7 @@
       <c r="F383"/>
       <c r="G383"/>
       <c r="H383" t="s">
-        <v>340</v>
+        <v>57</v>
       </c>
       <c r="I383"/>
       <c r="J383"/>
@@ -8743,7 +8569,7 @@
         <v>46022</v>
       </c>
       <c r="B384" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C384"/>
       <c r="D384"/>
@@ -8751,7 +8577,7 @@
       <c r="F384"/>
       <c r="G384"/>
       <c r="H384" t="s">
-        <v>341</v>
+        <v>198</v>
       </c>
       <c r="I384"/>
       <c r="J384"/>
@@ -8762,7 +8588,7 @@
         <v>46022</v>
       </c>
       <c r="B385" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C385"/>
       <c r="D385"/>
@@ -8770,7 +8596,7 @@
       <c r="F385"/>
       <c r="G385"/>
       <c r="H385" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="I385"/>
       <c r="J385"/>
@@ -8781,7 +8607,7 @@
         <v>46053</v>
       </c>
       <c r="B386" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C386"/>
       <c r="D386"/>
@@ -8789,7 +8615,7 @@
       <c r="F386"/>
       <c r="G386"/>
       <c r="H386" t="s">
-        <v>343</v>
+        <v>33</v>
       </c>
       <c r="I386"/>
       <c r="J386"/>
@@ -8800,7 +8626,7 @@
         <v>46053</v>
       </c>
       <c r="B387" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C387"/>
       <c r="D387"/>
@@ -8808,7 +8634,7 @@
       <c r="F387"/>
       <c r="G387"/>
       <c r="H387" t="s">
-        <v>344</v>
+        <v>32</v>
       </c>
       <c r="I387"/>
       <c r="J387"/>
@@ -8819,7 +8645,7 @@
         <v>46053</v>
       </c>
       <c r="B388" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C388"/>
       <c r="D388"/>
@@ -8827,7 +8653,7 @@
       <c r="F388"/>
       <c r="G388"/>
       <c r="H388" t="s">
-        <v>345</v>
+        <v>289</v>
       </c>
       <c r="I388"/>
       <c r="J388"/>
@@ -8838,7 +8664,7 @@
         <v>46053</v>
       </c>
       <c r="B389" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C389"/>
       <c r="D389"/>
@@ -8846,7 +8672,7 @@
       <c r="F389"/>
       <c r="G389"/>
       <c r="H389" t="s">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="I389"/>
       <c r="J389"/>
@@ -8865,7 +8691,7 @@
       <c r="F390"/>
       <c r="G390"/>
       <c r="H390" t="s">
-        <v>347</v>
+        <v>291</v>
       </c>
       <c r="I390"/>
       <c r="J390"/>
@@ -8884,7 +8710,7 @@
       <c r="F391"/>
       <c r="G391"/>
       <c r="H391" t="s">
-        <v>348</v>
+        <v>29</v>
       </c>
       <c r="I391"/>
       <c r="J391"/>
@@ -8903,7 +8729,7 @@
       <c r="F392"/>
       <c r="G392"/>
       <c r="H392" t="s">
-        <v>344</v>
+        <v>105</v>
       </c>
       <c r="I392"/>
       <c r="J392"/>
@@ -8922,7 +8748,7 @@
       <c r="F393"/>
       <c r="G393"/>
       <c r="H393" t="s">
-        <v>349</v>
+        <v>292</v>
       </c>
       <c r="I393"/>
       <c r="J393"/>
@@ -8933,7 +8759,7 @@
         <v>46112</v>
       </c>
       <c r="B394" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C394"/>
       <c r="D394"/>
@@ -8941,7 +8767,7 @@
       <c r="F394"/>
       <c r="G394"/>
       <c r="H394" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="I394"/>
       <c r="J394"/>
@@ -8952,7 +8778,7 @@
         <v>46112</v>
       </c>
       <c r="B395" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C395"/>
       <c r="D395"/>
@@ -8960,7 +8786,7 @@
       <c r="F395"/>
       <c r="G395"/>
       <c r="H395" t="s">
-        <v>350</v>
+        <v>130</v>
       </c>
       <c r="I395"/>
       <c r="J395"/>
@@ -8971,7 +8797,7 @@
         <v>46112</v>
       </c>
       <c r="B396" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C396"/>
       <c r="D396"/>
@@ -8979,7 +8805,7 @@
       <c r="F396"/>
       <c r="G396"/>
       <c r="H396" t="s">
-        <v>97</v>
+        <v>294</v>
       </c>
       <c r="I396"/>
       <c r="J396"/>
@@ -8998,7 +8824,7 @@
       <c r="F397"/>
       <c r="G397"/>
       <c r="H397" t="s">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="I397"/>
       <c r="J397"/>
@@ -9009,7 +8835,7 @@
         <v>46142</v>
       </c>
       <c r="B398" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C398"/>
       <c r="D398"/>
@@ -9017,7 +8843,7 @@
       <c r="F398"/>
       <c r="G398"/>
       <c r="H398" t="s">
-        <v>352</v>
+        <v>173</v>
       </c>
       <c r="I398"/>
       <c r="J398"/>
@@ -9028,7 +8854,7 @@
         <v>46142</v>
       </c>
       <c r="B399" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C399"/>
       <c r="D399"/>
@@ -9036,7 +8862,7 @@
       <c r="F399"/>
       <c r="G399"/>
       <c r="H399" t="s">
-        <v>353</v>
+        <v>296</v>
       </c>
       <c r="I399"/>
       <c r="J399"/>
@@ -9055,7 +8881,7 @@
       <c r="F400"/>
       <c r="G400"/>
       <c r="H400" t="s">
-        <v>48</v>
+        <v>204</v>
       </c>
       <c r="I400"/>
       <c r="J400"/>
@@ -9066,7 +8892,7 @@
         <v>46142</v>
       </c>
       <c r="B401" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C401"/>
       <c r="D401"/>
@@ -9074,7 +8900,7 @@
       <c r="F401"/>
       <c r="G401"/>
       <c r="H401" t="s">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="I401"/>
       <c r="J401"/>
